--- a/upload/taxa-readmissao-2025.xlsx
+++ b/upload/taxa-readmissao-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D658"/>
+  <dimension ref="A1:D665"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1549,7 +1549,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="3">
-        <v>1.9417475728155338E-2</v>
+        <v>2.1052631578947368E-2</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2445,7 +2445,7 @@
         <v>11</v>
       </c>
       <c r="D147" s="3">
-        <v>1.4084507042253521E-2</v>
+        <v>2.1126760563380281E-2</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3243,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="D204" s="3">
-        <v>9.5607235142118857E-2</v>
+        <v>9.585492227979274E-2</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3453,7 +3453,7 @@
         <v>12</v>
       </c>
       <c r="D219" s="3">
-        <v>3.2934131736526949E-2</v>
+        <v>3.2835820895522387E-2</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3495,21 +3495,21 @@
         <v>3</v>
       </c>
       <c r="D222" s="3">
-        <v>3.2608695652173912E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B223" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C223" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D223" s="3">
-        <v>3.5955056179775284E-2</v>
+        <v>3.4602076124567475E-3</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3520,10 +3520,10 @@
         <v>2020</v>
       </c>
       <c r="C224" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" s="3">
-        <v>1.3392857142857142E-2</v>
+        <v>3.5955056179775284E-2</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3534,10 +3534,10 @@
         <v>2020</v>
       </c>
       <c r="C225" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D225" s="3">
-        <v>7.0754716981132077E-3</v>
+        <v>1.3392857142857142E-2</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3548,10 +3548,10 @@
         <v>2020</v>
       </c>
       <c r="C226" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D226" s="3">
-        <v>2.0989505247376312E-2</v>
+        <v>7.0754716981132077E-3</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3562,10 +3562,10 @@
         <v>2020</v>
       </c>
       <c r="C227" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D227" s="3">
-        <v>2.828854314002829E-3</v>
+        <v>2.0989505247376312E-2</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3576,10 +3576,10 @@
         <v>2020</v>
       </c>
       <c r="C228" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D228" s="3">
-        <v>1.5015015015015015E-3</v>
+        <v>2.828854314002829E-3</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3590,10 +3590,10 @@
         <v>2020</v>
       </c>
       <c r="C229" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D229" s="3">
-        <v>7.7760497667185074E-3</v>
+        <v>1.5015015015015015E-3</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3604,10 +3604,10 @@
         <v>2020</v>
       </c>
       <c r="C230" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D230" s="3">
-        <v>1.2797074954296161E-2</v>
+        <v>7.7760497667185074E-3</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3618,10 +3618,10 @@
         <v>2020</v>
       </c>
       <c r="C231" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D231" s="3">
-        <v>1.7628205128205128E-2</v>
+        <v>1.2797074954296161E-2</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3632,10 +3632,10 @@
         <v>2020</v>
       </c>
       <c r="C232" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D232" s="3">
-        <v>2.1840873634945399E-2</v>
+        <v>1.7628205128205128E-2</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3646,10 +3646,10 @@
         <v>2020</v>
       </c>
       <c r="C233" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D233" s="3">
-        <v>1.282051282051282E-2</v>
+        <v>2.1840873634945399E-2</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3660,10 +3660,10 @@
         <v>2020</v>
       </c>
       <c r="C234" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D234" s="3">
-        <v>9.0361445783132526E-3</v>
+        <v>1.282051282051282E-2</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3671,13 +3671,13 @@
         <v>7</v>
       </c>
       <c r="B235" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C235" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D235" s="3">
-        <v>2.800658978583196E-2</v>
+        <v>9.0361445783132526E-3</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3688,10 +3688,10 @@
         <v>2021</v>
       </c>
       <c r="C236" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" s="3">
-        <v>1.384083044982699E-2</v>
+        <v>2.800658978583196E-2</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3702,10 +3702,10 @@
         <v>2021</v>
       </c>
       <c r="C237" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237" s="3">
-        <v>3.9630118890356669E-3</v>
+        <v>1.384083044982699E-2</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3716,10 +3716,10 @@
         <v>2021</v>
       </c>
       <c r="C238" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D238" s="3">
-        <v>4.9833887043189366E-3</v>
+        <v>3.9630118890356669E-3</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3730,10 +3730,10 @@
         <v>2021</v>
       </c>
       <c r="C239" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D239" s="3">
-        <v>8.291873963515755E-3</v>
+        <v>4.9833887043189366E-3</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3744,10 +3744,10 @@
         <v>2021</v>
       </c>
       <c r="C240" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D240" s="3">
-        <v>6.4829821717990272E-3</v>
+        <v>8.291873963515755E-3</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3758,10 +3758,10 @@
         <v>2021</v>
       </c>
       <c r="C241" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D241" s="3">
-        <v>1.3927576601671309E-2</v>
+        <v>6.4829821717990272E-3</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3772,10 +3772,10 @@
         <v>2021</v>
       </c>
       <c r="C242" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D242" s="3">
-        <v>1.3254786450662739E-2</v>
+        <v>1.3927576601671309E-2</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3786,10 +3786,10 @@
         <v>2021</v>
       </c>
       <c r="C243" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D243" s="3">
-        <v>2.0872865275142316E-2</v>
+        <v>1.3254786450662739E-2</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3800,10 +3800,10 @@
         <v>2021</v>
       </c>
       <c r="C244" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D244" s="3">
-        <v>1.5432098765432098E-2</v>
+        <v>2.0872865275142316E-2</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3814,10 +3814,10 @@
         <v>2021</v>
       </c>
       <c r="C245" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D245" s="3">
-        <v>2.0900321543408359E-2</v>
+        <v>1.5432098765432098E-2</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3828,10 +3828,10 @@
         <v>2021</v>
       </c>
       <c r="C246" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D246" s="3">
-        <v>1.6344725111441308E-2</v>
+        <v>2.0900321543408359E-2</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3839,13 +3839,13 @@
         <v>7</v>
       </c>
       <c r="B247" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C247" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D247" s="3">
-        <v>7.5075075075075074E-3</v>
+        <v>1.6344725111441308E-2</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3856,10 +3856,10 @@
         <v>2022</v>
       </c>
       <c r="C248" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248" s="3">
-        <v>1.5238095238095238E-2</v>
+        <v>7.5075075075075074E-3</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3870,10 +3870,10 @@
         <v>2022</v>
       </c>
       <c r="C249" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D249" s="3">
-        <v>2.6604068857589983E-2</v>
+        <v>1.5238095238095238E-2</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3884,10 +3884,10 @@
         <v>2022</v>
       </c>
       <c r="C250" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D250" s="3">
-        <v>3.8095238095238099E-2</v>
+        <v>2.6604068857589983E-2</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3898,10 +3898,10 @@
         <v>2022</v>
       </c>
       <c r="C251" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D251" s="3">
-        <v>1.238390092879257E-2</v>
+        <v>3.8095238095238099E-2</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3912,10 +3912,10 @@
         <v>2022</v>
       </c>
       <c r="C252" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3">
-        <v>9.7719869706840382E-3</v>
+        <v>1.238390092879257E-2</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3926,10 +3926,10 @@
         <v>2022</v>
       </c>
       <c r="C253" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D253" s="3">
-        <v>9.4191522762951327E-3</v>
+        <v>9.7719869706840382E-3</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3940,10 +3940,10 @@
         <v>2022</v>
       </c>
       <c r="C254" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D254" s="3">
-        <v>8.253094910591471E-3</v>
+        <v>9.4191522762951327E-3</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3954,10 +3954,10 @@
         <v>2022</v>
       </c>
       <c r="C255" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D255" s="3">
-        <v>1.0230179028132993E-2</v>
+        <v>8.253094910591471E-3</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3968,10 +3968,10 @@
         <v>2022</v>
       </c>
       <c r="C256" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D256" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>1.0230179028132993E-2</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3982,10 +3982,10 @@
         <v>2022</v>
       </c>
       <c r="C257" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D257" s="3">
-        <v>2.2091310751104567E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3996,10 +3996,10 @@
         <v>2022</v>
       </c>
       <c r="C258" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D258" s="3">
-        <v>2.5850340136054421E-2</v>
+        <v>2.2091310751104567E-2</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4007,13 +4007,13 @@
         <v>7</v>
       </c>
       <c r="B259" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C259" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D259" s="3">
-        <v>2.7656477438136828E-2</v>
+        <v>2.5850340136054421E-2</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4024,10 +4024,10 @@
         <v>2023</v>
       </c>
       <c r="C260" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" s="3">
-        <v>2.9957203994293864E-2</v>
+        <v>2.7656477438136828E-2</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4038,10 +4038,10 @@
         <v>2023</v>
       </c>
       <c r="C261" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D261" s="3">
-        <v>3.7712895377128956E-2</v>
+        <v>2.9957203994293864E-2</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4052,10 +4052,10 @@
         <v>2023</v>
       </c>
       <c r="C262" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262" s="3">
-        <v>4.3708609271523181E-2</v>
+        <v>3.7712895377128956E-2</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4066,10 +4066,10 @@
         <v>2023</v>
       </c>
       <c r="C263" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D263" s="3">
-        <v>2.1251475796930343E-2</v>
+        <v>4.3708609271523181E-2</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4080,10 +4080,10 @@
         <v>2023</v>
       </c>
       <c r="C264" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D264" s="3">
-        <v>2.7989821882951654E-2</v>
+        <v>2.1251475796930343E-2</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4094,10 +4094,10 @@
         <v>2023</v>
       </c>
       <c r="C265" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D265" s="3">
-        <v>2.442002442002442E-2</v>
+        <v>2.7989821882951654E-2</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4108,10 +4108,10 @@
         <v>2023</v>
       </c>
       <c r="C266" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D266" s="3">
-        <v>1.7488076311605722E-2</v>
+        <v>2.442002442002442E-2</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4122,10 +4122,10 @@
         <v>2023</v>
       </c>
       <c r="C267" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D267" s="3">
-        <v>1.3924050632911392E-2</v>
+        <v>1.7488076311605722E-2</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4136,10 +4136,10 @@
         <v>2023</v>
       </c>
       <c r="C268" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D268" s="3">
-        <v>1.3615733736762481E-2</v>
+        <v>1.3924050632911392E-2</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4150,10 +4150,10 @@
         <v>2023</v>
       </c>
       <c r="C269" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D269" s="3">
-        <v>2.3174971031286212E-2</v>
+        <v>1.3615733736762481E-2</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4164,10 +4164,10 @@
         <v>2023</v>
       </c>
       <c r="C270" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D270" s="3">
-        <v>2.7057497181510709E-2</v>
+        <v>2.3174971031286212E-2</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4175,13 +4175,13 @@
         <v>7</v>
       </c>
       <c r="B271" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C271" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D271" s="3">
-        <v>2.4608501118568233E-2</v>
+        <v>2.7057497181510709E-2</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4192,10 +4192,10 @@
         <v>2024</v>
       </c>
       <c r="C272" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D272" s="3">
-        <v>3.9314516129032258E-2</v>
+        <v>2.4608501118568233E-2</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4206,10 +4206,10 @@
         <v>2024</v>
       </c>
       <c r="C273" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D273" s="3">
-        <v>2.3907666941467436E-2</v>
+        <v>3.9314516129032258E-2</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4220,10 +4220,10 @@
         <v>2024</v>
       </c>
       <c r="C274" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D274" s="3">
-        <v>3.0755711775043937E-2</v>
+        <v>2.3907666941467436E-2</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4234,10 +4234,10 @@
         <v>2024</v>
       </c>
       <c r="C275" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D275" s="3">
-        <v>4.6968403074295471E-2</v>
+        <v>3.0755711775043937E-2</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4248,10 +4248,10 @@
         <v>2024</v>
       </c>
       <c r="C276" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D276" s="3">
-        <v>4.2056074766355138E-2</v>
+        <v>4.6968403074295471E-2</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4262,10 +4262,10 @@
         <v>2024</v>
       </c>
       <c r="C277" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D277" s="3">
-        <v>4.6168051708217916E-2</v>
+        <v>4.2056074766355138E-2</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4276,10 +4276,10 @@
         <v>2024</v>
       </c>
       <c r="C278" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D278" s="3">
-        <v>4.1121495327102804E-2</v>
+        <v>4.6168051708217916E-2</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4290,10 +4290,10 @@
         <v>2024</v>
       </c>
       <c r="C279" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D279" s="3">
-        <v>3.7401574803149609E-2</v>
+        <v>4.1121495327102804E-2</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4304,10 +4304,10 @@
         <v>2024</v>
       </c>
       <c r="C280" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D280" s="3">
-        <v>3.9413382218148489E-2</v>
+        <v>3.7401574803149609E-2</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4318,10 +4318,10 @@
         <v>2024</v>
       </c>
       <c r="C281" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D281" s="3">
-        <v>4.1666666666666664E-2</v>
+        <v>3.9413382218148489E-2</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4332,10 +4332,10 @@
         <v>2024</v>
       </c>
       <c r="C282" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D282" s="3">
-        <v>4.6095954844778929E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4343,13 +4343,13 @@
         <v>7</v>
       </c>
       <c r="B283" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C283" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D283" s="3">
-        <v>4.363636363636364E-2</v>
+        <v>4.6095954844778929E-2</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4360,10 +4360,10 @@
         <v>2025</v>
       </c>
       <c r="C284" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D284" s="3">
-        <v>3.536345776031434E-2</v>
+        <v>4.363636363636364E-2</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4374,10 +4374,10 @@
         <v>2025</v>
       </c>
       <c r="C285" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D285" s="3">
-        <v>2.5129982668977469E-2</v>
+        <v>3.536345776031434E-2</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4388,10 +4388,10 @@
         <v>2025</v>
       </c>
       <c r="C286" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D286" s="3">
-        <v>2.6459854014598539E-2</v>
+        <v>2.5129982668977469E-2</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4402,10 +4402,10 @@
         <v>2025</v>
       </c>
       <c r="C287" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D287" s="3">
-        <v>6.954102920723227E-3</v>
+        <v>2.7372262773722629E-2</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4416,10 +4416,10 @@
         <v>2025</v>
       </c>
       <c r="C288" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D288" s="3">
-        <v>4.5871559633027525E-3</v>
+        <v>1.1111111111111112E-2</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4430,10 +4430,10 @@
         <v>2025</v>
       </c>
       <c r="C289" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D289" s="3">
-        <v>2.5089605734767026E-2</v>
+        <v>1.1737089201877934E-2</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4444,10 +4444,10 @@
         <v>2025</v>
       </c>
       <c r="C290" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D290" s="3">
-        <v>1.7992424242424244E-2</v>
+        <v>2.5089605734767026E-2</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4458,10 +4458,10 @@
         <v>2025</v>
       </c>
       <c r="C291" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D291" s="3">
-        <v>3.2579185520361993E-2</v>
+        <v>1.7992424242424244E-2</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4472,10 +4472,10 @@
         <v>2025</v>
       </c>
       <c r="C292" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D292" s="3">
-        <v>1.3409961685823755E-2</v>
+        <v>3.2579185520361993E-2</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4486,10 +4486,10 @@
         <v>2025</v>
       </c>
       <c r="C293" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D293" s="3">
-        <v>3.7336024217961658E-2</v>
+        <v>1.3409961685823755E-2</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4500,10 +4500,10 @@
         <v>2025</v>
       </c>
       <c r="C294" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D294" s="3">
-        <v>1.5957446808510637E-2</v>
+        <v>3.7298387096774195E-2</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4511,13 +4511,13 @@
         <v>7</v>
       </c>
       <c r="B295" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C295" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D295" s="3">
-        <v>1.0840108401084011E-2</v>
+        <v>1.5957446808510637E-2</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4528,38 +4528,38 @@
         <v>2026</v>
       </c>
       <c r="C296" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D296" s="3">
-        <v>1.8450184501845018E-3</v>
+        <v>1.0840108401084011E-2</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B297" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C297" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D297" s="3">
-        <v>6.7114093959731542E-3</v>
+        <v>1.8450184501845018E-3</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B298" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C298" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D298" s="3">
-        <v>7.3349633251833741E-3</v>
+        <v>2.9895366218236174E-3</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4570,10 +4570,10 @@
         <v>2020</v>
       </c>
       <c r="C299" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D299" s="3">
-        <v>5.681818181818182E-3</v>
+        <v>6.7114093959731542E-3</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4584,10 +4584,10 @@
         <v>2020</v>
       </c>
       <c r="C300" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D300" s="3">
-        <v>1.5677491601343786E-2</v>
+        <v>7.3349633251833741E-3</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4598,10 +4598,10 @@
         <v>2020</v>
       </c>
       <c r="C301" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D301" s="3">
-        <v>1.1142061281337047E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4612,10 +4612,10 @@
         <v>2020</v>
       </c>
       <c r="C302" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D302" s="3">
-        <v>1.2154696132596685E-2</v>
+        <v>1.5677491601343786E-2</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4626,10 +4626,10 @@
         <v>2020</v>
       </c>
       <c r="C303" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D303" s="3">
-        <v>1.781970649895178E-2</v>
+        <v>1.1142061281337047E-2</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4640,10 +4640,10 @@
         <v>2020</v>
       </c>
       <c r="C304" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D304" s="3">
-        <v>1.4705882352941176E-2</v>
+        <v>1.2154696132596685E-2</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4654,10 +4654,10 @@
         <v>2020</v>
       </c>
       <c r="C305" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D305" s="3">
-        <v>9.4936708860759497E-3</v>
+        <v>1.781970649895178E-2</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4665,13 +4665,13 @@
         <v>8</v>
       </c>
       <c r="B306" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C306" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D306" s="3">
-        <v>3.6496350364963502E-3</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4679,13 +4679,13 @@
         <v>8</v>
       </c>
       <c r="B307" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C307" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D307" s="3">
-        <v>9.6463022508038593E-3</v>
+        <v>9.4936708860759497E-3</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4696,10 +4696,10 @@
         <v>2021</v>
       </c>
       <c r="C308" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D308" s="3">
-        <v>6.1349693251533744E-3</v>
+        <v>3.6496350364963502E-3</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4710,10 +4710,10 @@
         <v>2021</v>
       </c>
       <c r="C309" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D309" s="3">
-        <v>2.7355623100303952E-2</v>
+        <v>9.6463022508038593E-3</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4724,10 +4724,10 @@
         <v>2021</v>
       </c>
       <c r="C310" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D310" s="3">
-        <v>1.3490725126475547E-2</v>
+        <v>6.1349693251533744E-3</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4738,10 +4738,10 @@
         <v>2021</v>
       </c>
       <c r="C311" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D311" s="3">
-        <v>1.425438596491228E-2</v>
+        <v>2.7355623100303952E-2</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4752,10 +4752,10 @@
         <v>2021</v>
       </c>
       <c r="C312" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D312" s="3">
-        <v>2.2754491017964073E-2</v>
+        <v>1.3490725126475547E-2</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4766,10 +4766,10 @@
         <v>2021</v>
       </c>
       <c r="C313" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D313" s="3">
-        <v>2.8037383177570093E-2</v>
+        <v>1.425438596491228E-2</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4780,10 +4780,10 @@
         <v>2021</v>
       </c>
       <c r="C314" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D314" s="3">
-        <v>1.425438596491228E-2</v>
+        <v>2.2754491017964073E-2</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4794,10 +4794,10 @@
         <v>2021</v>
       </c>
       <c r="C315" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D315" s="3">
-        <v>2.3972602739726026E-2</v>
+        <v>2.8037383177570093E-2</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4808,10 +4808,10 @@
         <v>2021</v>
       </c>
       <c r="C316" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D316" s="3">
-        <v>2.430939226519337E-2</v>
+        <v>1.425438596491228E-2</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4819,13 +4819,13 @@
         <v>8</v>
       </c>
       <c r="B317" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C317" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D317" s="3">
-        <v>1.6797312430011199E-2</v>
+        <v>2.3972602739726026E-2</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4833,13 +4833,13 @@
         <v>8</v>
       </c>
       <c r="B318" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C318" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D318" s="3">
-        <v>3.0120481927710845E-3</v>
+        <v>2.430939226519337E-2</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4850,10 +4850,10 @@
         <v>2022</v>
       </c>
       <c r="C319" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D319" s="3">
-        <v>1.1098779134295227E-2</v>
+        <v>1.6797312430011199E-2</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4864,10 +4864,10 @@
         <v>2022</v>
       </c>
       <c r="C320" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D320" s="3">
-        <v>1.1574074074074073E-2</v>
+        <v>3.0120481927710845E-3</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4878,10 +4878,10 @@
         <v>2022</v>
       </c>
       <c r="C321" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D321" s="3">
-        <v>1.5606242496998799E-2</v>
+        <v>1.1098779134295227E-2</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4892,10 +4892,10 @@
         <v>2022</v>
       </c>
       <c r="C322" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D322" s="3">
-        <v>1.8610421836228287E-2</v>
+        <v>1.1574074074074073E-2</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4906,10 +4906,10 @@
         <v>2022</v>
       </c>
       <c r="C323" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D323" s="3">
-        <v>1.8478260869565218E-2</v>
+        <v>1.5606242496998799E-2</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4920,10 +4920,10 @@
         <v>2022</v>
       </c>
       <c r="C324" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D324" s="3">
-        <v>1.913265306122449E-2</v>
+        <v>1.8610421836228287E-2</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4934,10 +4934,10 @@
         <v>2022</v>
       </c>
       <c r="C325" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D325" s="3">
-        <v>2.6315789473684209E-2</v>
+        <v>1.8478260869565218E-2</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4948,10 +4948,10 @@
         <v>2022</v>
       </c>
       <c r="C326" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D326" s="3">
-        <v>1.7492711370262391E-2</v>
+        <v>1.913265306122449E-2</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4962,10 +4962,10 @@
         <v>2022</v>
       </c>
       <c r="C327" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D327" s="3">
-        <v>2.591283863368669E-2</v>
+        <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4976,10 +4976,10 @@
         <v>2022</v>
       </c>
       <c r="C328" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D328" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>1.7492711370262391E-2</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4987,13 +4987,13 @@
         <v>8</v>
       </c>
       <c r="B329" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C329" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D329" s="3">
-        <v>1.8369690011481057E-2</v>
+        <v>2.591283863368669E-2</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5001,13 +5001,13 @@
         <v>8</v>
       </c>
       <c r="B330" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C330" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D330" s="3">
-        <v>1.7456359102244388E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5018,10 +5018,10 @@
         <v>2023</v>
       </c>
       <c r="C331" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331" s="3">
-        <v>1.627906976744186E-2</v>
+        <v>1.8369690011481057E-2</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5032,10 +5032,10 @@
         <v>2023</v>
       </c>
       <c r="C332" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D332" s="3">
-        <v>1.8518518518518517E-2</v>
+        <v>1.7456359102244388E-2</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5046,10 +5046,10 @@
         <v>2023</v>
       </c>
       <c r="C333" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D333" s="3">
-        <v>2.0597322348094749E-2</v>
+        <v>1.627906976744186E-2</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5060,10 +5060,10 @@
         <v>2023</v>
       </c>
       <c r="C334" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D334" s="3">
-        <v>2.0111731843575419E-2</v>
+        <v>1.8518518518518517E-2</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5074,10 +5074,10 @@
         <v>2023</v>
       </c>
       <c r="C335" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D335" s="3">
-        <v>2.5945945945945945E-2</v>
+        <v>2.0597322348094749E-2</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5088,10 +5088,10 @@
         <v>2023</v>
       </c>
       <c r="C336" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D336" s="3">
-        <v>2.6709401709401708E-2</v>
+        <v>2.0111731843575419E-2</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5102,10 +5102,10 @@
         <v>2023</v>
       </c>
       <c r="C337" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D337" s="3">
-        <v>3.5087719298245612E-2</v>
+        <v>2.5945945945945945E-2</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5116,10 +5116,10 @@
         <v>2023</v>
       </c>
       <c r="C338" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D338" s="3">
-        <v>3.5460992907801421E-2</v>
+        <v>2.6709401709401708E-2</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5130,10 +5130,10 @@
         <v>2023</v>
       </c>
       <c r="C339" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D339" s="3">
-        <v>5.6928034371643392E-2</v>
+        <v>3.5087719298245612E-2</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5144,10 +5144,10 @@
         <v>2023</v>
       </c>
       <c r="C340" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D340" s="3">
-        <v>4.4979079497907949E-2</v>
+        <v>3.5460992907801421E-2</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5155,13 +5155,13 @@
         <v>8</v>
       </c>
       <c r="B341" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C341" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D341" s="3">
-        <v>3.7757437070938218E-2</v>
+        <v>5.6928034371643392E-2</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5169,13 +5169,13 @@
         <v>8</v>
       </c>
       <c r="B342" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C342" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D342" s="3">
-        <v>3.0092592592592591E-2</v>
+        <v>4.4979079497907949E-2</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5186,10 +5186,10 @@
         <v>2024</v>
       </c>
       <c r="C343" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D343" s="3">
-        <v>2.9439696106362774E-2</v>
+        <v>3.7757437070938218E-2</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5200,10 +5200,10 @@
         <v>2024</v>
       </c>
       <c r="C344" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D344" s="3">
-        <v>4.2074363992172209E-2</v>
+        <v>3.0092592592592591E-2</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5214,10 +5214,10 @@
         <v>2024</v>
       </c>
       <c r="C345" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D345" s="3">
-        <v>3.0274361400189215E-2</v>
+        <v>2.9439696106362774E-2</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5228,10 +5228,10 @@
         <v>2024</v>
       </c>
       <c r="C346" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D346" s="3">
-        <v>3.8014783526927137E-2</v>
+        <v>4.2074363992172209E-2</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5242,10 +5242,10 @@
         <v>2024</v>
       </c>
       <c r="C347" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D347" s="3">
-        <v>3.816046966731898E-2</v>
+        <v>3.0274361400189215E-2</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5256,10 +5256,10 @@
         <v>2024</v>
       </c>
       <c r="C348" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D348" s="3">
-        <v>2.3454157782515993E-2</v>
+        <v>3.8014783526927137E-2</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5270,10 +5270,10 @@
         <v>2024</v>
       </c>
       <c r="C349" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D349" s="3">
-        <v>2.3758099352051837E-2</v>
+        <v>3.816046966731898E-2</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5284,10 +5284,10 @@
         <v>2024</v>
       </c>
       <c r="C350" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D350" s="3">
-        <v>2.6776519052523172E-2</v>
+        <v>2.3454157782515993E-2</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5298,10 +5298,10 @@
         <v>2024</v>
       </c>
       <c r="C351" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D351" s="3">
-        <v>3.2186459489456157E-2</v>
+        <v>2.3758099352051837E-2</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5312,10 +5312,10 @@
         <v>2024</v>
       </c>
       <c r="C352" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D352" s="3">
-        <v>4.0363269424823413E-2</v>
+        <v>2.6776519052523172E-2</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5323,13 +5323,13 @@
         <v>8</v>
       </c>
       <c r="B353" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C353" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D353" s="3">
-        <v>2.0683453237410072E-2</v>
+        <v>3.2186459489456157E-2</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5337,13 +5337,13 @@
         <v>8</v>
       </c>
       <c r="B354" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C354" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D354" s="3">
-        <v>2.0942408376963352E-2</v>
+        <v>4.0363269424823413E-2</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5354,10 +5354,10 @@
         <v>2025</v>
       </c>
       <c r="C355" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D355" s="3">
-        <v>3.0476190476190476E-2</v>
+        <v>2.0683453237410072E-2</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5368,10 +5368,10 @@
         <v>2025</v>
       </c>
       <c r="C356" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D356" s="3">
-        <v>2.3255813953488372E-2</v>
+        <v>2.0942408376963352E-2</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5382,10 +5382,10 @@
         <v>2025</v>
       </c>
       <c r="C357" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D357" s="3">
-        <v>1.3774104683195593E-2</v>
+        <v>3.0476190476190476E-2</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5396,10 +5396,10 @@
         <v>2025</v>
       </c>
       <c r="C358" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D358" s="3">
-        <v>2.7255639097744359E-2</v>
+        <v>2.3255813953488372E-2</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5410,10 +5410,10 @@
         <v>2025</v>
       </c>
       <c r="C359" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D359" s="3">
-        <v>1.4367816091954023E-2</v>
+        <v>1.3774104683195593E-2</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5424,10 +5424,10 @@
         <v>2025</v>
       </c>
       <c r="C360" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D360" s="3">
-        <v>1.8115942028985508E-2</v>
+        <v>2.819548872180451E-2</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5438,10 +5438,10 @@
         <v>2025</v>
       </c>
       <c r="C361" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D361" s="3">
-        <v>2.1317829457364341E-2</v>
+        <v>1.4367816091954023E-2</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5452,10 +5452,10 @@
         <v>2025</v>
       </c>
       <c r="C362" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D362" s="3">
-        <v>1.7346053772766695E-2</v>
+        <v>1.8115942028985508E-2</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5466,10 +5466,10 @@
         <v>2025</v>
       </c>
       <c r="C363" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D363" s="3">
-        <v>1.9169329073482427E-2</v>
+        <v>2.133850630455868E-2</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5480,10 +5480,10 @@
         <v>2025</v>
       </c>
       <c r="C364" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D364" s="3">
-        <v>1.3432835820895522E-2</v>
+        <v>1.7346053772766695E-2</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5491,13 +5491,13 @@
         <v>8</v>
       </c>
       <c r="B365" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C365" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D365" s="3">
-        <v>1.2170385395537525E-2</v>
+        <v>2.3429179978700747E-2</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5505,13 +5505,13 @@
         <v>8</v>
       </c>
       <c r="B366" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C366" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D366" s="3">
-        <v>7.8125E-3</v>
+        <v>1.2206572769953052E-2</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5522,52 +5522,52 @@
         <v>2026</v>
       </c>
       <c r="C367" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D367" s="3">
-        <v>2.8089887640449437E-3</v>
+        <v>1.3171225937183385E-2</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B368" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C368" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D368" s="3">
-        <v>8.5470085470085479E-3</v>
+        <v>7.82122905027933E-3</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B369" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C369" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D369" s="3">
-        <v>1.7811704834605598E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B370" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C370" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3">
-        <v>1.9197207678883072E-2</v>
+        <v>1.9337016574585635E-2</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5578,10 +5578,10 @@
         <v>2019</v>
       </c>
       <c r="C371" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D371" s="3">
-        <v>4.307116104868914E-2</v>
+        <v>8.5470085470085479E-3</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5592,10 +5592,10 @@
         <v>2019</v>
       </c>
       <c r="C372" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D372" s="3">
-        <v>4.96031746031746E-2</v>
+        <v>1.7811704834605598E-2</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5606,10 +5606,10 @@
         <v>2019</v>
       </c>
       <c r="C373" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D373" s="3">
-        <v>3.5714285714285712E-2</v>
+        <v>1.9197207678883072E-2</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5620,10 +5620,10 @@
         <v>2019</v>
       </c>
       <c r="C374" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D374" s="3">
-        <v>6.4202334630350189E-2</v>
+        <v>4.307116104868914E-2</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5634,10 +5634,10 @@
         <v>2019</v>
       </c>
       <c r="C375" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D375" s="3">
-        <v>3.6458333333333336E-2</v>
+        <v>4.96031746031746E-2</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5645,13 +5645,13 @@
         <v>9</v>
       </c>
       <c r="B376" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C376" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D376" s="3">
-        <v>2.1848739495798318E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5659,13 +5659,13 @@
         <v>9</v>
       </c>
       <c r="B377" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C377" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D377" s="3">
-        <v>4.0336134453781515E-2</v>
+        <v>6.4202334630350189E-2</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5673,13 +5673,13 @@
         <v>9</v>
       </c>
       <c r="B378" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C378" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D378" s="3">
-        <v>3.5200000000000002E-2</v>
+        <v>3.6458333333333336E-2</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5690,10 +5690,10 @@
         <v>2020</v>
       </c>
       <c r="C379" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D379" s="3">
-        <v>4.3029259896729774E-2</v>
+        <v>2.1848739495798318E-2</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5704,10 +5704,10 @@
         <v>2020</v>
       </c>
       <c r="C380" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="3">
-        <v>5.6603773584905662E-2</v>
+        <v>4.0336134453781515E-2</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5718,10 +5718,10 @@
         <v>2020</v>
       </c>
       <c r="C381" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D381" s="3">
-        <v>5.6910569105691054E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5732,10 +5732,10 @@
         <v>2020</v>
       </c>
       <c r="C382" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D382" s="3">
-        <v>5.2953156822810592E-2</v>
+        <v>4.3029259896729774E-2</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5746,10 +5746,10 @@
         <v>2020</v>
       </c>
       <c r="C383" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D383" s="3">
-        <v>5.4393305439330547E-2</v>
+        <v>5.6603773584905662E-2</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5760,10 +5760,10 @@
         <v>2020</v>
       </c>
       <c r="C384" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D384" s="3">
-        <v>5.8585858585858588E-2</v>
+        <v>5.6910569105691054E-2</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5774,10 +5774,10 @@
         <v>2020</v>
       </c>
       <c r="C385" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D385" s="3">
-        <v>4.6747967479674794E-2</v>
+        <v>5.2953156822810592E-2</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5788,10 +5788,10 @@
         <v>2020</v>
       </c>
       <c r="C386" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D386" s="3">
-        <v>5.2083333333333336E-2</v>
+        <v>5.4393305439330547E-2</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5802,10 +5802,10 @@
         <v>2020</v>
       </c>
       <c r="C387" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D387" s="3">
-        <v>8.3333333333333329E-2</v>
+        <v>5.8585858585858588E-2</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5813,13 +5813,13 @@
         <v>9</v>
       </c>
       <c r="B388" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C388" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D388" s="3">
-        <v>3.8535645472061654E-2</v>
+        <v>4.6747967479674794E-2</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5827,13 +5827,13 @@
         <v>9</v>
       </c>
       <c r="B389" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C389" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D389" s="3">
-        <v>2.7726432532347505E-2</v>
+        <v>5.2083333333333336E-2</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5841,13 +5841,13 @@
         <v>9</v>
       </c>
       <c r="B390" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C390" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D390" s="3">
-        <v>4.5375218150087257E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5858,10 +5858,10 @@
         <v>2021</v>
       </c>
       <c r="C391" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D391" s="3">
-        <v>4.7463175122749592E-2</v>
+        <v>3.8535645472061654E-2</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5872,10 +5872,10 @@
         <v>2021</v>
       </c>
       <c r="C392" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D392" s="3">
-        <v>4.0219378427787937E-2</v>
+        <v>2.7726432532347505E-2</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5886,10 +5886,10 @@
         <v>2021</v>
       </c>
       <c r="C393" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D393" s="3">
-        <v>3.8181818181818185E-2</v>
+        <v>4.5375218150087257E-2</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5900,10 +5900,10 @@
         <v>2021</v>
       </c>
       <c r="C394" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D394" s="3">
-        <v>3.5825545171339561E-2</v>
+        <v>4.7463175122749592E-2</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5914,10 +5914,10 @@
         <v>2021</v>
       </c>
       <c r="C395" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D395" s="3">
-        <v>2.7210884353741496E-2</v>
+        <v>4.0219378427787937E-2</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5928,10 +5928,10 @@
         <v>2021</v>
       </c>
       <c r="C396" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D396" s="3">
-        <v>3.8142620232172471E-2</v>
+        <v>3.8181818181818185E-2</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5942,10 +5942,10 @@
         <v>2021</v>
       </c>
       <c r="C397" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D397" s="3">
-        <v>3.041144901610018E-2</v>
+        <v>3.5825545171339561E-2</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5956,10 +5956,10 @@
         <v>2021</v>
       </c>
       <c r="C398" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D398" s="3">
-        <v>3.4071550255536626E-2</v>
+        <v>2.7210884353741496E-2</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5970,10 +5970,10 @@
         <v>2021</v>
       </c>
       <c r="C399" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D399" s="3">
-        <v>2.5210084033613446E-2</v>
+        <v>3.8142620232172471E-2</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -5981,13 +5981,13 @@
         <v>9</v>
       </c>
       <c r="B400" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C400" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D400" s="3">
-        <v>2.5454545454545455E-2</v>
+        <v>3.041144901610018E-2</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -5995,13 +5995,13 @@
         <v>9</v>
       </c>
       <c r="B401" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C401" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D401" s="3">
-        <v>3.5523978685612786E-2</v>
+        <v>3.4071550255536626E-2</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6009,13 +6009,13 @@
         <v>9</v>
       </c>
       <c r="B402" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C402" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D402" s="3">
-        <v>2.9411764705882353E-2</v>
+        <v>2.5210084033613446E-2</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6026,10 +6026,10 @@
         <v>2022</v>
       </c>
       <c r="C403" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D403" s="3">
-        <v>2.6604068857589983E-2</v>
+        <v>2.5454545454545455E-2</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6040,10 +6040,10 @@
         <v>2022</v>
       </c>
       <c r="C404" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D404" s="3">
-        <v>3.6163522012578615E-2</v>
+        <v>3.5523978685612786E-2</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6054,10 +6054,10 @@
         <v>2022</v>
       </c>
       <c r="C405" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D405" s="3">
-        <v>4.0584415584415584E-2</v>
+        <v>2.9411764705882353E-2</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6068,10 +6068,10 @@
         <v>2022</v>
       </c>
       <c r="C406" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D406" s="3">
-        <v>3.2786885245901641E-2</v>
+        <v>2.6604068857589983E-2</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6082,10 +6082,10 @@
         <v>2022</v>
       </c>
       <c r="C407" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D407" s="3">
-        <v>3.7096774193548385E-2</v>
+        <v>3.6163522012578615E-2</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6096,10 +6096,10 @@
         <v>2022</v>
       </c>
       <c r="C408" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D408" s="3">
-        <v>4.716981132075472E-2</v>
+        <v>4.0584415584415584E-2</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6110,10 +6110,10 @@
         <v>2022</v>
       </c>
       <c r="C409" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D409" s="3">
-        <v>3.3457249070631967E-2</v>
+        <v>3.2786885245901641E-2</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6124,10 +6124,10 @@
         <v>2022</v>
       </c>
       <c r="C410" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D410" s="3">
-        <v>3.6912751677852351E-2</v>
+        <v>3.7096774193548385E-2</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6138,10 +6138,10 @@
         <v>2022</v>
       </c>
       <c r="C411" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D411" s="3">
-        <v>2.6711185308848081E-2</v>
+        <v>4.716981132075472E-2</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6149,13 +6149,13 @@
         <v>9</v>
       </c>
       <c r="B412" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C412" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D412" s="3">
-        <v>3.1914893617021274E-2</v>
+        <v>3.3457249070631967E-2</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6163,13 +6163,13 @@
         <v>9</v>
       </c>
       <c r="B413" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C413" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D413" s="3">
-        <v>1.9064124783362217E-2</v>
+        <v>3.6912751677852351E-2</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6177,13 +6177,13 @@
         <v>9</v>
       </c>
       <c r="B414" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C414" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D414" s="3">
-        <v>3.2400589101620032E-2</v>
+        <v>2.6711185308848081E-2</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6194,10 +6194,10 @@
         <v>2023</v>
       </c>
       <c r="C415" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D415" s="3">
-        <v>2.1739130434782608E-2</v>
+        <v>3.1914893617021274E-2</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6208,10 +6208,10 @@
         <v>2023</v>
       </c>
       <c r="C416" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D416" s="3">
-        <v>2.923076923076923E-2</v>
+        <v>1.9064124783362217E-2</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6222,10 +6222,10 @@
         <v>2023</v>
       </c>
       <c r="C417" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D417" s="3">
-        <v>2.0437956204379562E-2</v>
+        <v>3.2400589101620032E-2</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6236,10 +6236,10 @@
         <v>2023</v>
       </c>
       <c r="C418" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D418" s="3">
-        <v>2.5723472668810289E-2</v>
+        <v>2.1739130434782608E-2</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6250,10 +6250,10 @@
         <v>2023</v>
       </c>
       <c r="C419" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D419" s="3">
-        <v>2.2968197879858657E-2</v>
+        <v>2.923076923076923E-2</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6264,10 +6264,10 @@
         <v>2023</v>
       </c>
       <c r="C420" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D420" s="3">
-        <v>3.39943342776204E-2</v>
+        <v>2.0437956204379562E-2</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6278,10 +6278,10 @@
         <v>2023</v>
       </c>
       <c r="C421" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D421" s="3">
-        <v>1.7391304347826087E-2</v>
+        <v>2.5723472668810289E-2</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6292,10 +6292,10 @@
         <v>2023</v>
       </c>
       <c r="C422" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D422" s="3">
-        <v>4.2483660130718956E-2</v>
+        <v>2.2968197879858657E-2</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6306,10 +6306,10 @@
         <v>2023</v>
       </c>
       <c r="C423" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D423" s="3">
-        <v>3.5561877667140827E-2</v>
+        <v>3.39943342776204E-2</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6317,13 +6317,13 @@
         <v>9</v>
       </c>
       <c r="B424" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C424" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D424" s="3">
-        <v>2.5974025974025976E-2</v>
+        <v>1.7391304347826087E-2</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6331,13 +6331,13 @@
         <v>9</v>
       </c>
       <c r="B425" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C425" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D425" s="3">
-        <v>2.823920265780731E-2</v>
+        <v>4.2483660130718956E-2</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6345,13 +6345,13 @@
         <v>9</v>
       </c>
       <c r="B426" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C426" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D426" s="3">
-        <v>1.2949640287769784E-2</v>
+        <v>3.5561877667140827E-2</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6362,10 +6362,10 @@
         <v>2024</v>
       </c>
       <c r="C427" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D427" s="3">
-        <v>1.5673981191222569E-2</v>
+        <v>2.5974025974025976E-2</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6376,10 +6376,10 @@
         <v>2024</v>
       </c>
       <c r="C428" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D428" s="3">
-        <v>2.8106508875739646E-2</v>
+        <v>2.823920265780731E-2</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6390,10 +6390,10 @@
         <v>2024</v>
       </c>
       <c r="C429" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D429" s="3">
-        <v>2.4844720496894408E-2</v>
+        <v>1.2949640287769784E-2</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6404,10 +6404,10 @@
         <v>2024</v>
       </c>
       <c r="C430" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D430" s="3">
-        <v>4.4478527607361963E-2</v>
+        <v>1.5673981191222569E-2</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6418,10 +6418,10 @@
         <v>2024</v>
       </c>
       <c r="C431" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D431" s="3">
-        <v>2.6912181303116147E-2</v>
+        <v>2.8106508875739646E-2</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6432,10 +6432,10 @@
         <v>2024</v>
       </c>
       <c r="C432" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D432" s="3">
-        <v>3.3236994219653176E-2</v>
+        <v>2.4844720496894408E-2</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6446,10 +6446,10 @@
         <v>2024</v>
       </c>
       <c r="C433" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D433" s="3">
-        <v>3.287671232876712E-2</v>
+        <v>4.4478527607361963E-2</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6460,10 +6460,10 @@
         <v>2024</v>
       </c>
       <c r="C434" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D434" s="3">
-        <v>1.849217638691323E-2</v>
+        <v>2.6912181303116147E-2</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6474,10 +6474,10 @@
         <v>2024</v>
       </c>
       <c r="C435" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D435" s="3">
-        <v>2.0270270270270271E-2</v>
+        <v>3.3236994219653176E-2</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6485,13 +6485,13 @@
         <v>9</v>
       </c>
       <c r="B436" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C436" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D436" s="3">
-        <v>2.3809523809523808E-2</v>
+        <v>3.287671232876712E-2</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6499,13 +6499,13 @@
         <v>9</v>
       </c>
       <c r="B437" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C437" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D437" s="3">
-        <v>1.6742770167427701E-2</v>
+        <v>1.849217638691323E-2</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6513,13 +6513,13 @@
         <v>9</v>
       </c>
       <c r="B438" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C438" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D438" s="3">
-        <v>2.9891304347826088E-2</v>
+        <v>2.0270270270270271E-2</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6530,10 +6530,10 @@
         <v>2025</v>
       </c>
       <c r="C439" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D439" s="3">
-        <v>4.9019607843137254E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6544,10 +6544,10 @@
         <v>2025</v>
       </c>
       <c r="C440" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D440" s="3">
-        <v>3.1157270029673591E-2</v>
+        <v>1.6742770167427701E-2</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6558,10 +6558,10 @@
         <v>2025</v>
       </c>
       <c r="C441" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D441" s="3">
-        <v>1.9858156028368795E-2</v>
+        <v>2.9891304347826088E-2</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6572,10 +6572,10 @@
         <v>2025</v>
       </c>
       <c r="C442" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D442" s="3">
-        <v>1.0810810810810811E-2</v>
+        <v>4.9019607843137254E-2</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6586,10 +6586,10 @@
         <v>2025</v>
       </c>
       <c r="C443" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D443" s="3">
-        <v>1.2640449438202247E-2</v>
+        <v>3.1157270029673591E-2</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6600,10 +6600,10 @@
         <v>2025</v>
       </c>
       <c r="C444" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D444" s="3">
-        <v>1.2391573729863693E-2</v>
+        <v>1.9858156028368795E-2</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6614,10 +6614,10 @@
         <v>2025</v>
       </c>
       <c r="C445" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D445" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>1.0810810810810811E-2</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6628,10 +6628,10 @@
         <v>2025</v>
       </c>
       <c r="C446" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D446" s="3">
-        <v>7.8125E-3</v>
+        <v>1.2640449438202247E-2</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6642,10 +6642,10 @@
         <v>2025</v>
       </c>
       <c r="C447" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D447" s="3">
-        <v>6.7842605156037995E-3</v>
+        <v>1.2391573729863693E-2</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6653,13 +6653,13 @@
         <v>9</v>
       </c>
       <c r="B448" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C448" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D448" s="3">
-        <v>1.2484394506866416E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6667,13 +6667,13 @@
         <v>9</v>
       </c>
       <c r="B449" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C449" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D449" s="3">
-        <v>2.8530670470756064E-3</v>
+        <v>7.8125E-3</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6681,69 +6681,69 @@
         <v>9</v>
       </c>
       <c r="B450" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C450" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D450" s="3">
-        <v>1.0269576379974325E-2</v>
+        <v>6.7842605156037995E-3</v>
       </c>
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B451" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C451" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D451" s="3">
-        <v>1.9801980198019802E-2</v>
+        <v>1.2484394506866416E-2</v>
       </c>
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B452" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C452" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D452" s="3">
-        <v>1</v>
+        <v>2.8530670470756064E-3</v>
       </c>
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B453" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C453" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D453" s="3">
-        <v>4.878048780487805E-2</v>
+        <v>1.1538461538461539E-2</v>
       </c>
     </row>
     <row r="454" spans="1:4">
       <c r="A454" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B454" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C454" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D454" s="3">
-        <v>2.030456852791878E-2</v>
+        <v>3.8610038610038611E-3</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6751,13 +6751,13 @@
         <v>10</v>
       </c>
       <c r="B455" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C455" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D455" s="3">
-        <v>3.6842105263157891E-2</v>
+        <v>1.9801980198019802E-2</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6768,10 +6768,10 @@
         <v>2020</v>
       </c>
       <c r="C456" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D456" s="3">
-        <v>2.7777777777777776E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6782,10 +6782,10 @@
         <v>2020</v>
       </c>
       <c r="C457" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D457" s="3">
-        <v>5.5214723926380369E-2</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6796,10 +6796,10 @@
         <v>2020</v>
       </c>
       <c r="C458" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D458" s="3">
-        <v>4.0540540540540543E-2</v>
+        <v>2.030456852791878E-2</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6810,10 +6810,10 @@
         <v>2020</v>
       </c>
       <c r="C459" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D459" s="3">
-        <v>1.935483870967742E-2</v>
+        <v>3.6842105263157891E-2</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6821,13 +6821,13 @@
         <v>10</v>
       </c>
       <c r="B460" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C460" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D460" s="3">
-        <v>3.4482758620689655E-2</v>
+        <v>2.7777777777777776E-2</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6835,13 +6835,13 @@
         <v>10</v>
       </c>
       <c r="B461" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C461" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D461" s="3">
-        <v>2.7972027972027972E-2</v>
+        <v>5.5214723926380369E-2</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6849,13 +6849,13 @@
         <v>10</v>
       </c>
       <c r="B462" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C462" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D462" s="3">
-        <v>3.5294117647058823E-2</v>
+        <v>4.0540540540540543E-2</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6863,13 +6863,13 @@
         <v>10</v>
       </c>
       <c r="B463" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C463" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D463" s="3">
-        <v>2.8571428571428571E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6880,10 +6880,10 @@
         <v>2021</v>
       </c>
       <c r="C464" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D464" s="3">
-        <v>1.1049723756906077E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6894,10 +6894,10 @@
         <v>2021</v>
       </c>
       <c r="C465" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D465" s="3">
-        <v>3.8674033149171269E-2</v>
+        <v>2.7972027972027972E-2</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6908,10 +6908,10 @@
         <v>2021</v>
       </c>
       <c r="C466" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D466" s="3">
-        <v>6.3157894736842107E-2</v>
+        <v>3.5294117647058823E-2</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6922,10 +6922,10 @@
         <v>2021</v>
       </c>
       <c r="C467" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D467" s="3">
-        <v>3.4090909090909088E-2</v>
+        <v>2.8571428571428571E-2</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6936,10 +6936,10 @@
         <v>2021</v>
       </c>
       <c r="C468" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D468" s="3">
-        <v>3.7735849056603772E-2</v>
+        <v>1.1049723756906077E-2</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6950,10 +6950,10 @@
         <v>2021</v>
       </c>
       <c r="C469" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D469" s="3">
-        <v>4.1916167664670656E-2</v>
+        <v>3.8674033149171269E-2</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6964,10 +6964,10 @@
         <v>2021</v>
       </c>
       <c r="C470" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D470" s="3">
-        <v>3.5175879396984924E-2</v>
+        <v>6.3157894736842107E-2</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6978,10 +6978,10 @@
         <v>2021</v>
       </c>
       <c r="C471" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D471" s="3">
-        <v>6.2857142857142861E-2</v>
+        <v>3.4090909090909088E-2</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6989,13 +6989,13 @@
         <v>10</v>
       </c>
       <c r="B472" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C472" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D472" s="3">
-        <v>2.1917808219178082E-2</v>
+        <v>3.7735849056603772E-2</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7003,13 +7003,13 @@
         <v>10</v>
       </c>
       <c r="B473" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C473" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D473" s="3">
-        <v>2.9239766081871343E-2</v>
+        <v>4.1916167664670656E-2</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7017,13 +7017,13 @@
         <v>10</v>
       </c>
       <c r="B474" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C474" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D474" s="3">
-        <v>4.1095890410958902E-2</v>
+        <v>3.5175879396984924E-2</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7031,13 +7031,13 @@
         <v>10</v>
       </c>
       <c r="B475" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C475" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D475" s="3">
-        <v>6.2893081761006293E-3</v>
+        <v>6.2857142857142861E-2</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7048,10 +7048,10 @@
         <v>2022</v>
       </c>
       <c r="C476" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D476" s="3">
-        <v>2.0270270270270271E-2</v>
+        <v>2.1917808219178082E-2</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7062,10 +7062,10 @@
         <v>2022</v>
       </c>
       <c r="C477" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D477" s="3">
-        <v>2.5773195876288658E-2</v>
+        <v>2.9239766081871343E-2</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7076,10 +7076,10 @@
         <v>2022</v>
       </c>
       <c r="C478" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D478" s="3">
-        <v>3.7634408602150539E-2</v>
+        <v>4.1095890410958902E-2</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7090,10 +7090,10 @@
         <v>2022</v>
       </c>
       <c r="C479" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D479" s="3">
-        <v>2.247191011235955E-2</v>
+        <v>6.2893081761006293E-3</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7104,10 +7104,10 @@
         <v>2022</v>
       </c>
       <c r="C480" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D480" s="3">
-        <v>3.0120481927710843E-2</v>
+        <v>2.0270270270270271E-2</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7118,10 +7118,10 @@
         <v>2022</v>
       </c>
       <c r="C481" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D481" s="3">
-        <v>1.3422818791946308E-2</v>
+        <v>2.5773195876288658E-2</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7132,10 +7132,10 @@
         <v>2022</v>
       </c>
       <c r="C482" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D482" s="3">
-        <v>2.2857142857142857E-2</v>
+        <v>3.7634408602150539E-2</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7143,13 +7143,13 @@
         <v>10</v>
       </c>
       <c r="B483" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C483" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D483" s="3">
-        <v>3.9325842696629212E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7157,13 +7157,13 @@
         <v>10</v>
       </c>
       <c r="B484" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C484" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D484" s="3">
-        <v>1.9607843137254902E-2</v>
+        <v>3.0120481927710843E-2</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7171,13 +7171,13 @@
         <v>10</v>
       </c>
       <c r="B485" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C485" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D485" s="3">
-        <v>3.3112582781456956E-2</v>
+        <v>1.3422818791946308E-2</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7185,13 +7185,13 @@
         <v>10</v>
       </c>
       <c r="B486" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C486" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D486" s="3">
-        <v>2.247191011235955E-2</v>
+        <v>2.2857142857142857E-2</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7202,10 +7202,10 @@
         <v>2023</v>
       </c>
       <c r="C487" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D487" s="3">
-        <v>3.0864197530864196E-2</v>
+        <v>3.9325842696629212E-2</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7216,10 +7216,10 @@
         <v>2023</v>
       </c>
       <c r="C488" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D488" s="3">
-        <v>4.3956043956043959E-2</v>
+        <v>1.9607843137254902E-2</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7230,10 +7230,10 @@
         <v>2023</v>
       </c>
       <c r="C489" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D489" s="3">
-        <v>3.5714285714285712E-2</v>
+        <v>3.3112582781456956E-2</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7244,10 +7244,10 @@
         <v>2023</v>
       </c>
       <c r="C490" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D490" s="3">
-        <v>0.04</v>
+        <v>2.247191011235955E-2</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7258,10 +7258,10 @@
         <v>2023</v>
       </c>
       <c r="C491" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D491" s="3">
-        <v>2.2598870056497175E-2</v>
+        <v>3.0864197530864196E-2</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7272,10 +7272,10 @@
         <v>2023</v>
       </c>
       <c r="C492" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D492" s="3">
-        <v>3.0864197530864196E-2</v>
+        <v>4.3956043956043959E-2</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7286,10 +7286,10 @@
         <v>2023</v>
       </c>
       <c r="C493" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D493" s="3">
-        <v>7.3529411764705885E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7300,10 +7300,10 @@
         <v>2023</v>
       </c>
       <c r="C494" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D494" s="3">
-        <v>2.4875621890547265E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7311,13 +7311,13 @@
         <v>10</v>
       </c>
       <c r="B495" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C495" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D495" s="3">
-        <v>2.2522522522522521E-2</v>
+        <v>2.2598870056497175E-2</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7325,13 +7325,13 @@
         <v>10</v>
       </c>
       <c r="B496" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C496" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D496" s="3">
-        <v>3.1413612565445025E-2</v>
+        <v>3.0864197530864196E-2</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7339,13 +7339,13 @@
         <v>10</v>
       </c>
       <c r="B497" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C497" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D497" s="3">
-        <v>3.6649214659685861E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7353,13 +7353,13 @@
         <v>10</v>
       </c>
       <c r="B498" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C498" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D498" s="3">
-        <v>2.6178010471204188E-2</v>
+        <v>2.4875621890547265E-2</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7370,10 +7370,10 @@
         <v>2024</v>
       </c>
       <c r="C499" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D499" s="3">
-        <v>3.9408866995073892E-2</v>
+        <v>2.2522522522522521E-2</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7384,10 +7384,10 @@
         <v>2024</v>
       </c>
       <c r="C500" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D500" s="3">
-        <v>1.2195121951219513E-2</v>
+        <v>3.1413612565445025E-2</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7398,10 +7398,10 @@
         <v>2024</v>
       </c>
       <c r="C501" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D501" s="3">
-        <v>6.2500000000000003E-3</v>
+        <v>3.6649214659685861E-2</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7412,10 +7412,10 @@
         <v>2024</v>
       </c>
       <c r="C502" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D502" s="3">
-        <v>5.3191489361702126E-3</v>
+        <v>2.6178010471204188E-2</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7426,10 +7426,10 @@
         <v>2024</v>
       </c>
       <c r="C503" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D503" s="3">
-        <v>1.1627906976744186E-2</v>
+        <v>3.9408866995073892E-2</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7440,10 +7440,10 @@
         <v>2024</v>
       </c>
       <c r="C504" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D504" s="3">
-        <v>3.9215686274509803E-3</v>
+        <v>1.2195121951219513E-2</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7451,13 +7451,13 @@
         <v>10</v>
       </c>
       <c r="B505" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C505" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D505" s="3">
-        <v>1.1857707509881422E-2</v>
+        <v>6.2500000000000003E-3</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7465,13 +7465,13 @@
         <v>10</v>
       </c>
       <c r="B506" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C506" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D506" s="3">
-        <v>4.1322314049586778E-3</v>
+        <v>5.3191489361702126E-3</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7479,13 +7479,13 @@
         <v>10</v>
       </c>
       <c r="B507" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C507" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D507" s="3">
-        <v>4.0650406504065045E-3</v>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7493,13 +7493,13 @@
         <v>10</v>
       </c>
       <c r="B508" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C508" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D508" s="3">
-        <v>4.1666666666666666E-3</v>
+        <v>3.9215686274509803E-3</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7510,10 +7510,10 @@
         <v>2025</v>
       </c>
       <c r="C509" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D509" s="3">
-        <v>3.787878787878788E-3</v>
+        <v>1.1857707509881422E-2</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7524,10 +7524,10 @@
         <v>2025</v>
       </c>
       <c r="C510" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D510" s="3">
-        <v>8.2644628099173556E-3</v>
+        <v>4.1322314049586778E-3</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7538,10 +7538,10 @@
         <v>2025</v>
       </c>
       <c r="C511" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D511" s="3">
-        <v>4.464285714285714E-3</v>
+        <v>4.0650406504065045E-3</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7552,10 +7552,10 @@
         <v>2025</v>
       </c>
       <c r="C512" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D512" s="3">
-        <v>4.8780487804878049E-3</v>
+        <v>4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7563,83 +7563,83 @@
         <v>10</v>
       </c>
       <c r="B513" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C513" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D513" s="3">
-        <v>1.1764705882352941E-2</v>
+        <v>3.787878787878788E-3</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B514" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C514" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D514" s="3">
-        <v>7.4257425742574254E-3</v>
+        <v>8.2644628099173556E-3</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B515" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C515" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D515" s="3">
-        <v>7.6335877862595417E-3</v>
+        <v>4.464285714285714E-3</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B516" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C516" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D516" s="3">
-        <v>1.2987012987012988E-2</v>
+        <v>4.8780487804878049E-3</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B517" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C517" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D517" s="3">
-        <v>2.2388059701492536E-2</v>
+        <v>1.1764705882352941E-2</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B518" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C518" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D518" s="3">
-        <v>9.74025974025974E-3</v>
+        <v>8.0321285140562242E-3</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7650,10 +7650,10 @@
         <v>2020</v>
       </c>
       <c r="C519" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D519" s="3">
-        <v>1.1267605633802818E-2</v>
+        <v>7.4257425742574254E-3</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7664,10 +7664,10 @@
         <v>2020</v>
       </c>
       <c r="C520" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D520" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>7.6335877862595417E-3</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7678,10 +7678,10 @@
         <v>2020</v>
       </c>
       <c r="C521" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D521" s="3">
-        <v>1.7291066282420751E-2</v>
+        <v>1.2987012987012988E-2</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7692,10 +7692,10 @@
         <v>2020</v>
       </c>
       <c r="C522" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D522" s="3">
-        <v>1.65016501650165E-2</v>
+        <v>2.2388059701492536E-2</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7706,10 +7706,10 @@
         <v>2020</v>
       </c>
       <c r="C523" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D523" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>9.74025974025974E-3</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7720,10 +7720,10 @@
         <v>2020</v>
       </c>
       <c r="C524" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D524" s="3">
-        <v>1.3745704467353952E-2</v>
+        <v>1.1267605633802818E-2</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7731,13 +7731,13 @@
         <v>11</v>
       </c>
       <c r="B525" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C525" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D525" s="3">
-        <v>1.11731843575419E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7745,13 +7745,13 @@
         <v>11</v>
       </c>
       <c r="B526" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C526" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D526" s="3">
-        <v>7.6335877862595417E-3</v>
+        <v>1.7291066282420751E-2</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7759,13 +7759,13 @@
         <v>11</v>
       </c>
       <c r="B527" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C527" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D527" s="3">
-        <v>2.8301886792452831E-2</v>
+        <v>1.65016501650165E-2</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7773,13 +7773,13 @@
         <v>11</v>
       </c>
       <c r="B528" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C528" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D528" s="3">
-        <v>1.1933174224343675E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7787,13 +7787,13 @@
         <v>11</v>
       </c>
       <c r="B529" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C529" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D529" s="3">
-        <v>5.5096418732782371E-3</v>
+        <v>1.3745704467353952E-2</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7804,10 +7804,10 @@
         <v>2021</v>
       </c>
       <c r="C530" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D530" s="3">
-        <v>1.2048192771084338E-2</v>
+        <v>1.11731843575419E-2</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7818,10 +7818,10 @@
         <v>2021</v>
       </c>
       <c r="C531" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D531" s="3">
-        <v>1.5290519877675841E-2</v>
+        <v>7.6335877862595417E-3</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7832,10 +7832,10 @@
         <v>2021</v>
       </c>
       <c r="C532" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D532" s="3">
-        <v>5.6497175141242938E-3</v>
+        <v>2.8301886792452831E-2</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7846,10 +7846,10 @@
         <v>2021</v>
       </c>
       <c r="C533" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D533" s="3">
-        <v>1.2269938650306749E-2</v>
+        <v>1.1933174224343675E-2</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7860,10 +7860,10 @@
         <v>2021</v>
       </c>
       <c r="C534" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D534" s="3">
-        <v>1.7543859649122806E-2</v>
+        <v>5.5096418732782371E-3</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7874,10 +7874,10 @@
         <v>2021</v>
       </c>
       <c r="C535" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D535" s="3">
-        <v>2.4464831804281346E-2</v>
+        <v>1.2048192771084338E-2</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7888,10 +7888,10 @@
         <v>2021</v>
       </c>
       <c r="C536" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D536" s="3">
-        <v>1.5544041450777202E-2</v>
+        <v>1.5290519877675841E-2</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7899,13 +7899,13 @@
         <v>11</v>
       </c>
       <c r="B537" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C537" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D537" s="3">
-        <v>7.6142131979695434E-3</v>
+        <v>5.6497175141242938E-3</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7913,13 +7913,13 @@
         <v>11</v>
       </c>
       <c r="B538" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C538" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D538" s="3">
-        <v>1.1049723756906077E-2</v>
+        <v>1.2269938650306749E-2</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7927,13 +7927,13 @@
         <v>11</v>
       </c>
       <c r="B539" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C539" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D539" s="3">
-        <v>1.912568306010929E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7941,13 +7941,13 @@
         <v>11</v>
       </c>
       <c r="B540" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C540" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D540" s="3">
-        <v>1.9021739130434784E-2</v>
+        <v>2.4464831804281346E-2</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7955,13 +7955,13 @@
         <v>11</v>
       </c>
       <c r="B541" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C541" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D541" s="3">
-        <v>1.8421052631578946E-2</v>
+        <v>1.5544041450777202E-2</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7972,10 +7972,10 @@
         <v>2022</v>
       </c>
       <c r="C542" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D542" s="3">
-        <v>2.9508196721311476E-2</v>
+        <v>7.6142131979695434E-3</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7986,10 +7986,10 @@
         <v>2022</v>
       </c>
       <c r="C543" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D543" s="3">
-        <v>2.3809523809523808E-2</v>
+        <v>1.1049723756906077E-2</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -8000,10 +8000,10 @@
         <v>2022</v>
       </c>
       <c r="C544" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D544" s="3">
-        <v>1.2562814070351759E-2</v>
+        <v>1.912568306010929E-2</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8014,10 +8014,10 @@
         <v>2022</v>
       </c>
       <c r="C545" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D545" s="3">
-        <v>1.2106537530266344E-2</v>
+        <v>1.9021739130434784E-2</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8028,10 +8028,10 @@
         <v>2022</v>
       </c>
       <c r="C546" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D546" s="3">
-        <v>1.6085790884718499E-2</v>
+        <v>1.8421052631578946E-2</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8042,10 +8042,10 @@
         <v>2022</v>
       </c>
       <c r="C547" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D547" s="3">
-        <v>7.9787234042553185E-3</v>
+        <v>2.9508196721311476E-2</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8056,10 +8056,10 @@
         <v>2022</v>
       </c>
       <c r="C548" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D548" s="3">
-        <v>3.0959752321981426E-3</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8067,13 +8067,13 @@
         <v>11</v>
       </c>
       <c r="B549" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C549" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D549" s="3">
-        <v>5.8651026392961877E-3</v>
+        <v>1.2562814070351759E-2</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8081,13 +8081,13 @@
         <v>11</v>
       </c>
       <c r="B550" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C550" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D550" s="3">
-        <v>1.9498607242339833E-2</v>
+        <v>1.2106537530266344E-2</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8095,13 +8095,13 @@
         <v>11</v>
       </c>
       <c r="B551" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C551" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D551" s="3">
-        <v>9.852216748768473E-3</v>
+        <v>1.6085790884718499E-2</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8109,13 +8109,13 @@
         <v>11</v>
       </c>
       <c r="B552" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C552" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D552" s="3">
-        <v>2.0833333333333332E-2</v>
+        <v>7.9787234042553185E-3</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8123,13 +8123,13 @@
         <v>11</v>
       </c>
       <c r="B553" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C553" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D553" s="3">
-        <v>2.3419203747072601E-2</v>
+        <v>3.0959752321981426E-3</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8140,10 +8140,10 @@
         <v>2023</v>
       </c>
       <c r="C554" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D554" s="3">
-        <v>1.8181818181818181E-2</v>
+        <v>5.8651026392961877E-3</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8154,10 +8154,10 @@
         <v>2023</v>
       </c>
       <c r="C555" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D555" s="3">
-        <v>1.5151515151515152E-2</v>
+        <v>1.9498607242339833E-2</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8168,10 +8168,10 @@
         <v>2023</v>
       </c>
       <c r="C556" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D556" s="3">
-        <v>2.1028037383177569E-2</v>
+        <v>9.852216748768473E-3</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8182,10 +8182,10 @@
         <v>2023</v>
       </c>
       <c r="C557" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D557" s="3">
-        <v>2.6128266033254157E-2</v>
+        <v>2.0833333333333332E-2</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8196,10 +8196,10 @@
         <v>2023</v>
       </c>
       <c r="C558" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D558" s="3">
-        <v>1.1600928074245939E-2</v>
+        <v>2.3419203747072601E-2</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8210,10 +8210,10 @@
         <v>2023</v>
       </c>
       <c r="C559" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D559" s="3">
-        <v>1.3698630136986301E-2</v>
+        <v>1.8181818181818181E-2</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8224,10 +8224,10 @@
         <v>2023</v>
       </c>
       <c r="C560" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D560" s="3">
-        <v>2.4330900243309004E-2</v>
+        <v>1.5151515151515152E-2</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8235,13 +8235,13 @@
         <v>11</v>
       </c>
       <c r="B561" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C561" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D561" s="3">
-        <v>0.02</v>
+        <v>2.1028037383177569E-2</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8249,13 +8249,13 @@
         <v>11</v>
       </c>
       <c r="B562" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C562" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D562" s="3">
-        <v>3.1630170316301706E-2</v>
+        <v>2.6128266033254157E-2</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8263,13 +8263,13 @@
         <v>11</v>
       </c>
       <c r="B563" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C563" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D563" s="3">
-        <v>2.9473684210526315E-2</v>
+        <v>1.1600928074245939E-2</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8277,13 +8277,13 @@
         <v>11</v>
       </c>
       <c r="B564" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C564" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D564" s="3">
-        <v>1.4981273408239701E-2</v>
+        <v>1.3698630136986301E-2</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8291,13 +8291,13 @@
         <v>11</v>
       </c>
       <c r="B565" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C565" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D565" s="3">
-        <v>2.1568627450980392E-2</v>
+        <v>2.4330900243309004E-2</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8308,10 +8308,10 @@
         <v>2024</v>
       </c>
       <c r="C566" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D566" s="3">
-        <v>1.2474012474012475E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8322,10 +8322,10 @@
         <v>2024</v>
       </c>
       <c r="C567" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D567" s="3">
-        <v>2.9279279279279279E-2</v>
+        <v>3.1630170316301706E-2</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8336,10 +8336,10 @@
         <v>2024</v>
       </c>
       <c r="C568" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D568" s="3">
-        <v>1.8518518518518517E-2</v>
+        <v>2.9473684210526315E-2</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8350,10 +8350,10 @@
         <v>2024</v>
       </c>
       <c r="C569" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D569" s="3">
-        <v>2.0661157024793389E-2</v>
+        <v>1.4981273408239701E-2</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8364,10 +8364,10 @@
         <v>2024</v>
       </c>
       <c r="C570" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D570" s="3">
-        <v>2.7472527472527472E-2</v>
+        <v>2.1568627450980392E-2</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8378,10 +8378,10 @@
         <v>2024</v>
       </c>
       <c r="C571" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D571" s="3">
-        <v>1.3245033112582781E-2</v>
+        <v>1.2474012474012475E-2</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8392,10 +8392,10 @@
         <v>2024</v>
       </c>
       <c r="C572" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D572" s="3">
-        <v>1.4251781472684086E-2</v>
+        <v>2.9279279279279279E-2</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8403,13 +8403,13 @@
         <v>11</v>
       </c>
       <c r="B573" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C573" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D573" s="3">
-        <v>1.8957345971563982E-2</v>
+        <v>1.8518518518518517E-2</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8417,13 +8417,13 @@
         <v>11</v>
       </c>
       <c r="B574" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C574" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D574" s="3">
-        <v>1.8099547511312219E-2</v>
+        <v>2.0661157024793389E-2</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8431,13 +8431,13 @@
         <v>11</v>
       </c>
       <c r="B575" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C575" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D575" s="3">
-        <v>3.5650623885918001E-3</v>
+        <v>2.7472527472527472E-2</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8445,13 +8445,13 @@
         <v>11</v>
       </c>
       <c r="B576" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C576" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D576" s="3">
-        <v>3.616636528028933E-3</v>
+        <v>1.3245033112582781E-2</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8459,13 +8459,13 @@
         <v>11</v>
       </c>
       <c r="B577" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C577" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D577" s="3">
-        <v>3.3333333333333335E-3</v>
+        <v>1.4251781472684086E-2</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8476,10 +8476,10 @@
         <v>2025</v>
       </c>
       <c r="C578" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D578" s="3">
-        <v>1.8621973929236499E-3</v>
+        <v>1.8957345971563982E-2</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8490,10 +8490,10 @@
         <v>2025</v>
       </c>
       <c r="C579" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D579" s="3">
-        <v>5.5762081784386614E-3</v>
+        <v>1.8099547511312219E-2</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8504,10 +8504,10 @@
         <v>2025</v>
       </c>
       <c r="C580" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D580" s="3">
-        <v>1.3565891472868217E-2</v>
+        <v>3.5650623885918001E-3</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8518,10 +8518,10 @@
         <v>2025</v>
       </c>
       <c r="C581" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D581" s="3">
-        <v>5.4644808743169399E-3</v>
+        <v>3.616636528028933E-3</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8532,10 +8532,10 @@
         <v>2025</v>
       </c>
       <c r="C582" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D582" s="3">
-        <v>5.905511811023622E-3</v>
+        <v>3.3333333333333335E-3</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8546,10 +8546,10 @@
         <v>2025</v>
       </c>
       <c r="C583" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D583" s="3">
-        <v>6.1099796334012219E-3</v>
+        <v>1.8621973929236499E-3</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8557,13 +8557,13 @@
         <v>11</v>
       </c>
       <c r="B584" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C584" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D584" s="3">
-        <v>1.3544018058690745E-2</v>
+        <v>5.5762081784386614E-3</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8571,97 +8571,97 @@
         <v>11</v>
       </c>
       <c r="B585" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C585" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D585" s="3">
-        <v>8.4033613445378148E-3</v>
+        <v>1.3565891472868217E-2</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B586" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C586" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D586" s="3">
-        <v>6.024096385542169E-3</v>
+        <v>5.4644808743169399E-3</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B587" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C587" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D587" s="3">
-        <v>1.2750455373406194E-2</v>
+        <v>5.905511811023622E-3</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B588" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C588" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D588" s="3">
-        <v>5.1679586563307496E-3</v>
+        <v>6.1099796334012219E-3</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B589" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C589" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D589" s="3">
-        <v>8.6830680173661367E-3</v>
+        <v>1.3544018058690745E-2</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B590" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C590" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D590" s="3">
-        <v>1.1661807580174927E-2</v>
+        <v>6.3157894736842104E-3</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B591" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C591" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D591" s="3">
-        <v>6.2305295950155761E-3</v>
+        <v>2.1141649048625794E-3</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8669,13 +8669,13 @@
         <v>12</v>
       </c>
       <c r="B592" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C592" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D592" s="3">
-        <v>1.466275659824047E-2</v>
+        <v>6.024096385542169E-3</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8683,13 +8683,13 @@
         <v>12</v>
       </c>
       <c r="B593" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C593" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D593" s="3">
-        <v>3.5714285714285713E-3</v>
+        <v>1.2750455373406194E-2</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8697,13 +8697,13 @@
         <v>12</v>
       </c>
       <c r="B594" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C594" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D594" s="3">
-        <v>6.8143100511073255E-3</v>
+        <v>5.1679586563307496E-3</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8711,13 +8711,13 @@
         <v>12</v>
       </c>
       <c r="B595" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C595" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D595" s="3">
-        <v>7.4074074074074077E-3</v>
+        <v>8.6830680173661367E-3</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8725,13 +8725,13 @@
         <v>12</v>
       </c>
       <c r="B596" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C596" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D596" s="3">
-        <v>1.437699680511182E-2</v>
+        <v>1.1661807580174927E-2</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8742,10 +8742,10 @@
         <v>2020</v>
       </c>
       <c r="C597" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D597" s="3">
-        <v>1.002004008016032E-2</v>
+        <v>6.2305295950155761E-3</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8753,13 +8753,13 @@
         <v>12</v>
       </c>
       <c r="B598" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C598" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D598" s="3">
-        <v>1.751592356687898E-2</v>
+        <v>1.466275659824047E-2</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8767,13 +8767,13 @@
         <v>12</v>
       </c>
       <c r="B599" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C599" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D599" s="3">
-        <v>4.807692307692308E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8781,13 +8781,13 @@
         <v>12</v>
       </c>
       <c r="B600" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C600" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D600" s="3">
-        <v>7.3529411764705881E-3</v>
+        <v>6.8143100511073255E-3</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8795,13 +8795,13 @@
         <v>12</v>
       </c>
       <c r="B601" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C601" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D601" s="3">
-        <v>1.3235294117647059E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8809,13 +8809,13 @@
         <v>12</v>
       </c>
       <c r="B602" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C602" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D602" s="3">
-        <v>1.1283497884344146E-2</v>
+        <v>1.437699680511182E-2</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8823,13 +8823,13 @@
         <v>12</v>
       </c>
       <c r="B603" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C603" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D603" s="3">
-        <v>8.8757396449704144E-3</v>
+        <v>1.002004008016032E-2</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8840,10 +8840,10 @@
         <v>2021</v>
       </c>
       <c r="C604" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D604" s="3">
-        <v>8.9020771513353119E-3</v>
+        <v>1.751592356687898E-2</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8854,10 +8854,10 @@
         <v>2021</v>
       </c>
       <c r="C605" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D605" s="3">
-        <v>9.3833780160857902E-3</v>
+        <v>4.807692307692308E-3</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8868,10 +8868,10 @@
         <v>2021</v>
       </c>
       <c r="C606" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D606" s="3">
-        <v>7.462686567164179E-3</v>
+        <v>7.3529411764705881E-3</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8882,10 +8882,10 @@
         <v>2021</v>
       </c>
       <c r="C607" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D607" s="3">
-        <v>5.008347245409015E-3</v>
+        <v>1.3235294117647059E-2</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8896,10 +8896,10 @@
         <v>2021</v>
       </c>
       <c r="C608" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D608" s="3">
-        <v>1.9969278033794162E-2</v>
+        <v>1.1283497884344146E-2</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8910,10 +8910,10 @@
         <v>2021</v>
       </c>
       <c r="C609" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D609" s="3">
-        <v>1.3953488372093023E-2</v>
+        <v>8.8757396449704144E-3</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8921,13 +8921,13 @@
         <v>12</v>
       </c>
       <c r="B610" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C610" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D610" s="3">
-        <v>1.8867924528301886E-2</v>
+        <v>8.9020771513353119E-3</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8935,13 +8935,13 @@
         <v>12</v>
       </c>
       <c r="B611" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C611" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D611" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>9.3833780160857902E-3</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8949,13 +8949,13 @@
         <v>12</v>
       </c>
       <c r="B612" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C612" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D612" s="3">
-        <v>1.7725258493353029E-2</v>
+        <v>7.462686567164179E-3</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8963,13 +8963,13 @@
         <v>12</v>
       </c>
       <c r="B613" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C613" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D613" s="3">
-        <v>5.1020408163265302E-3</v>
+        <v>5.008347245409015E-3</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8977,13 +8977,13 @@
         <v>12</v>
       </c>
       <c r="B614" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C614" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D614" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>1.9969278033794162E-2</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8991,13 +8991,13 @@
         <v>12</v>
       </c>
       <c r="B615" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C615" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D615" s="3">
-        <v>1.5015015015015015E-2</v>
+        <v>1.3953488372093023E-2</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9008,10 +9008,10 @@
         <v>2022</v>
       </c>
       <c r="C616" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D616" s="3">
-        <v>2.0558002936857563E-2</v>
+        <v>1.8867924528301886E-2</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9022,10 +9022,10 @@
         <v>2022</v>
       </c>
       <c r="C617" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D617" s="3">
-        <v>1.2965964343598054E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9036,10 +9036,10 @@
         <v>2022</v>
       </c>
       <c r="C618" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D618" s="3">
-        <v>1.7828200972447326E-2</v>
+        <v>1.7725258493353029E-2</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9050,10 +9050,10 @@
         <v>2022</v>
       </c>
       <c r="C619" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D619" s="3">
-        <v>2.1885521885521887E-2</v>
+        <v>5.1020408163265302E-3</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9064,10 +9064,10 @@
         <v>2022</v>
       </c>
       <c r="C620" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D620" s="3">
-        <v>1.2965964343598054E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9078,10 +9078,10 @@
         <v>2022</v>
       </c>
       <c r="C621" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D621" s="3">
-        <v>1.6296296296296295E-2</v>
+        <v>1.5015015015015015E-2</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9089,13 +9089,13 @@
         <v>12</v>
       </c>
       <c r="B622" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C622" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D622" s="3">
-        <v>1.3910355486862442E-2</v>
+        <v>2.0558002936857563E-2</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9103,13 +9103,13 @@
         <v>12</v>
       </c>
       <c r="B623" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C623" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D623" s="3">
-        <v>1.4516129032258065E-2</v>
+        <v>1.2965964343598054E-2</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9117,13 +9117,13 @@
         <v>12</v>
       </c>
       <c r="B624" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C624" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D624" s="3">
-        <v>1.9920318725099601E-2</v>
+        <v>1.7828200972447326E-2</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9131,13 +9131,13 @@
         <v>12</v>
       </c>
       <c r="B625" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C625" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D625" s="3">
-        <v>1.2213740458015267E-2</v>
+        <v>2.1885521885521887E-2</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9145,13 +9145,13 @@
         <v>12</v>
       </c>
       <c r="B626" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C626" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D626" s="3">
-        <v>1.8018018018018018E-2</v>
+        <v>1.2965964343598054E-2</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9159,13 +9159,13 @@
         <v>12</v>
       </c>
       <c r="B627" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C627" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D627" s="3">
-        <v>2.0689655172413793E-2</v>
+        <v>1.6296296296296295E-2</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9176,10 +9176,10 @@
         <v>2023</v>
       </c>
       <c r="C628" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D628" s="3">
-        <v>1.4598540145985401E-2</v>
+        <v>1.3910355486862442E-2</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9190,10 +9190,10 @@
         <v>2023</v>
       </c>
       <c r="C629" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D629" s="3">
-        <v>1.9886363636363636E-2</v>
+        <v>1.4516129032258065E-2</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9204,10 +9204,10 @@
         <v>2023</v>
       </c>
       <c r="C630" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D630" s="3">
-        <v>1.9345238095238096E-2</v>
+        <v>1.9920318725099601E-2</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9218,10 +9218,10 @@
         <v>2023</v>
       </c>
       <c r="C631" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D631" s="3">
-        <v>2.5920873124147339E-2</v>
+        <v>1.2213740458015267E-2</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9232,10 +9232,10 @@
         <v>2023</v>
       </c>
       <c r="C632" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D632" s="3">
-        <v>2.4011299435028249E-2</v>
+        <v>1.8018018018018018E-2</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9246,10 +9246,10 @@
         <v>2023</v>
       </c>
       <c r="C633" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D633" s="3">
-        <v>2.2818791946308724E-2</v>
+        <v>2.0689655172413793E-2</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9257,13 +9257,13 @@
         <v>12</v>
       </c>
       <c r="B634" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C634" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D634" s="3">
-        <v>1.7804154302670624E-2</v>
+        <v>1.4598540145985401E-2</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9271,13 +9271,13 @@
         <v>12</v>
       </c>
       <c r="B635" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C635" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D635" s="3">
-        <v>1.2569832402234637E-2</v>
+        <v>1.9886363636363636E-2</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9285,13 +9285,13 @@
         <v>12</v>
       </c>
       <c r="B636" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C636" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D636" s="3">
-        <v>2.564102564102564E-2</v>
+        <v>1.9345238095238096E-2</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9299,13 +9299,13 @@
         <v>12</v>
       </c>
       <c r="B637" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C637" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D637" s="3">
-        <v>2.7027027027027029E-2</v>
+        <v>2.5920873124147339E-2</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9313,13 +9313,13 @@
         <v>12</v>
       </c>
       <c r="B638" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C638" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D638" s="3">
-        <v>2.0915032679738561E-2</v>
+        <v>2.4011299435028249E-2</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9327,13 +9327,13 @@
         <v>12</v>
       </c>
       <c r="B639" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C639" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D639" s="3">
-        <v>2.3952095808383235E-2</v>
+        <v>2.2818791946308724E-2</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9344,10 +9344,10 @@
         <v>2024</v>
       </c>
       <c r="C640" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D640" s="3">
-        <v>2.1551724137931036E-2</v>
+        <v>1.7804154302670624E-2</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9358,10 +9358,10 @@
         <v>2024</v>
       </c>
       <c r="C641" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D641" s="3">
-        <v>2.6315789473684209E-2</v>
+        <v>1.2569832402234637E-2</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9372,10 +9372,10 @@
         <v>2024</v>
       </c>
       <c r="C642" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D642" s="3">
-        <v>9.2592592592592587E-3</v>
+        <v>2.564102564102564E-2</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9386,10 +9386,10 @@
         <v>2024</v>
       </c>
       <c r="C643" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D643" s="3">
-        <v>7.7279752704791345E-3</v>
+        <v>2.7027027027027029E-2</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9400,10 +9400,10 @@
         <v>2024</v>
       </c>
       <c r="C644" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D644" s="3">
-        <v>6.5359477124183009E-3</v>
+        <v>2.0915032679738561E-2</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9414,10 +9414,10 @@
         <v>2024</v>
       </c>
       <c r="C645" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D645" s="3">
-        <v>1.0835913312693499E-2</v>
+        <v>2.3952095808383235E-2</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9425,13 +9425,13 @@
         <v>12</v>
       </c>
       <c r="B646" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C646" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D646" s="3">
-        <v>7.3099415204678359E-3</v>
+        <v>2.1551724137931036E-2</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9439,13 +9439,13 @@
         <v>12</v>
       </c>
       <c r="B647" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C647" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D647" s="3">
-        <v>1.0852713178294573E-2</v>
+        <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9453,13 +9453,13 @@
         <v>12</v>
       </c>
       <c r="B648" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C648" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D648" s="3">
-        <v>6.2893081761006293E-3</v>
+        <v>9.2592592592592587E-3</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9467,13 +9467,13 @@
         <v>12</v>
       </c>
       <c r="B649" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C649" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D649" s="3">
-        <v>7.7821011673151752E-3</v>
+        <v>7.7279752704791345E-3</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9481,13 +9481,13 @@
         <v>12</v>
       </c>
       <c r="B650" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C650" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D650" s="3">
-        <v>2.4330900243309003E-3</v>
+        <v>6.5359477124183009E-3</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9495,13 +9495,13 @@
         <v>12</v>
       </c>
       <c r="B651" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C651" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D651" s="3">
-        <v>6.6844919786096255E-3</v>
+        <v>1.0835913312693499E-2</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9512,10 +9512,10 @@
         <v>2025</v>
       </c>
       <c r="C652" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D652" s="3">
-        <v>3.0769230769230769E-3</v>
+        <v>7.3099415204678359E-3</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9526,10 +9526,10 @@
         <v>2025</v>
       </c>
       <c r="C653" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D653" s="3">
-        <v>5.6497175141242938E-3</v>
+        <v>1.0852713178294573E-2</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9540,10 +9540,10 @@
         <v>2025</v>
       </c>
       <c r="C654" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D654" s="3">
-        <v>1.1283497884344146E-2</v>
+        <v>6.2893081761006293E-3</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9554,10 +9554,10 @@
         <v>2025</v>
       </c>
       <c r="C655" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D655" s="3">
-        <v>8.658008658008658E-3</v>
+        <v>7.7821011673151752E-3</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9568,10 +9568,10 @@
         <v>2025</v>
       </c>
       <c r="C656" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D656" s="3">
-        <v>7.2992700729927005E-3</v>
+        <v>2.4330900243309003E-3</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -9579,13 +9579,13 @@
         <v>12</v>
       </c>
       <c r="B657" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C657" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D657" s="3">
-        <v>2.8571428571428571E-3</v>
+        <v>6.6844919786096255E-3</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -9593,13 +9593,111 @@
         <v>12</v>
       </c>
       <c r="B658" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C658" s="2">
+        <v>8</v>
+      </c>
+      <c r="D658" s="3">
+        <v>3.0769230769230769E-3</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4">
+      <c r="A659" t="s">
+        <v>12</v>
+      </c>
+      <c r="B659" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C659" s="2">
+        <v>9</v>
+      </c>
+      <c r="D659" s="3">
+        <v>5.6497175141242938E-3</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4">
+      <c r="A660" t="s">
+        <v>12</v>
+      </c>
+      <c r="B660" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C660" s="2">
+        <v>10</v>
+      </c>
+      <c r="D660" s="3">
+        <v>1.1283497884344146E-2</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4">
+      <c r="A661" t="s">
+        <v>12</v>
+      </c>
+      <c r="B661" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C661" s="2">
+        <v>11</v>
+      </c>
+      <c r="D661" s="3">
+        <v>8.658008658008658E-3</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4">
+      <c r="A662" t="s">
+        <v>12</v>
+      </c>
+      <c r="B662" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C662" s="2">
+        <v>12</v>
+      </c>
+      <c r="D662" s="3">
+        <v>8.5106382978723406E-3</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4">
+      <c r="A663" t="s">
+        <v>12</v>
+      </c>
+      <c r="B663" s="2">
         <v>2026</v>
       </c>
-      <c r="C658" s="2">
+      <c r="C663" s="2">
+        <v>1</v>
+      </c>
+      <c r="D663" s="3">
+        <v>2.8050490883590462E-3</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4">
+      <c r="A664" t="s">
+        <v>12</v>
+      </c>
+      <c r="B664" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C664" s="2">
         <v>2</v>
       </c>
-      <c r="D658" s="3">
-        <v>1.4326647564469914E-3</v>
+      <c r="D664" s="3">
+        <v>1.4306151645207439E-3</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4">
+      <c r="A665" t="s">
+        <v>12</v>
+      </c>
+      <c r="B665" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C665" s="2">
+        <v>3</v>
+      </c>
+      <c r="D665" s="3">
+        <v>2.5706940874035988E-3</v>
       </c>
     </row>
   </sheetData>

--- a/upload/taxa-readmissao-2025.xlsx
+++ b/upload/taxa-readmissao-2025.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D665"/>
+  <dimension ref="A1:D673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1409,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="D73" s="3">
-        <v>0.10452961672473868</v>
+        <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2453,13 +2453,13 @@
         <v>5</v>
       </c>
       <c r="B148" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D148" s="3">
-        <v>1.4388489208633094E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2470,38 +2470,38 @@
         <v>2026</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="3">
-        <v>7.5187969924812026E-3</v>
+        <v>1.4492753623188406E-2</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B150" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C150" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D150" s="3">
-        <v>9.3896713615023476E-3</v>
+        <v>7.5187969924812026E-3</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B151" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C151" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151" s="3">
-        <v>2.1201413427561839E-2</v>
+        <v>6.1349693251533744E-3</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2509,13 +2509,13 @@
         <v>6</v>
       </c>
       <c r="B152" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C152" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D152" s="3">
-        <v>9.4637223974763408E-3</v>
+        <v>9.3896713615023476E-3</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2526,10 +2526,10 @@
         <v>2020</v>
       </c>
       <c r="C153" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D153" s="3">
-        <v>7.407407407407407E-2</v>
+        <v>2.1201413427561839E-2</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2540,10 +2540,10 @@
         <v>2020</v>
       </c>
       <c r="C154" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D154" s="3">
-        <v>1.1627906976744186E-2</v>
+        <v>9.4637223974763408E-3</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2554,10 +2554,10 @@
         <v>2020</v>
       </c>
       <c r="C155" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D155" s="3">
-        <v>5.4794520547945206E-3</v>
+        <v>7.407407407407407E-2</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2568,10 +2568,10 @@
         <v>2020</v>
       </c>
       <c r="C156" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D156" s="3">
-        <v>1.9607843137254902E-2</v>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2582,10 +2582,10 @@
         <v>2020</v>
       </c>
       <c r="C157" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D157" s="3">
-        <v>1.7857142857142856E-2</v>
+        <v>5.4794520547945206E-3</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2596,10 +2596,10 @@
         <v>2020</v>
       </c>
       <c r="C158" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D158" s="3">
-        <v>1.0309278350515464E-2</v>
+        <v>1.9607843137254902E-2</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2610,10 +2610,10 @@
         <v>2020</v>
       </c>
       <c r="C159" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D159" s="3">
-        <v>1.1904761904761904E-2</v>
+        <v>1.7857142857142856E-2</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2624,10 +2624,10 @@
         <v>2020</v>
       </c>
       <c r="C160" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D160" s="3">
-        <v>1.2048192771084338E-2</v>
+        <v>1.0309278350515464E-2</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2635,13 +2635,13 @@
         <v>6</v>
       </c>
       <c r="B161" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C161" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D161" s="3">
-        <v>1.8927444794952682E-2</v>
+        <v>1.1904761904761904E-2</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2649,13 +2649,13 @@
         <v>6</v>
       </c>
       <c r="B162" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C162" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D162" s="3">
-        <v>2.4844720496894408E-2</v>
+        <v>1.2048192771084338E-2</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2666,10 +2666,10 @@
         <v>2021</v>
       </c>
       <c r="C163" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3">
-        <v>3.246753246753247E-3</v>
+        <v>1.8927444794952682E-2</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2680,10 +2680,10 @@
         <v>2021</v>
       </c>
       <c r="C164" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D164" s="3">
-        <v>3.4042553191489362E-2</v>
+        <v>2.4844720496894408E-2</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2694,10 +2694,10 @@
         <v>2021</v>
       </c>
       <c r="C165" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D165" s="3">
-        <v>1.7543859649122806E-2</v>
+        <v>3.246753246753247E-3</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2708,10 +2708,10 @@
         <v>2021</v>
       </c>
       <c r="C166" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D166" s="3">
-        <v>4.6439628482972138E-2</v>
+        <v>3.4042553191489362E-2</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2722,10 +2722,10 @@
         <v>2021</v>
       </c>
       <c r="C167" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D167" s="3">
-        <v>4.9019607843137254E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2736,10 +2736,10 @@
         <v>2021</v>
       </c>
       <c r="C168" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D168" s="3">
-        <v>3.2544378698224852E-2</v>
+        <v>4.6439628482972138E-2</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2750,10 +2750,10 @@
         <v>2021</v>
       </c>
       <c r="C169" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D169" s="3">
-        <v>7.18232044198895E-2</v>
+        <v>4.9019607843137254E-2</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2764,10 +2764,10 @@
         <v>2021</v>
       </c>
       <c r="C170" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D170" s="3">
-        <v>5.5401662049861494E-2</v>
+        <v>3.2544378698224852E-2</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2778,10 +2778,10 @@
         <v>2021</v>
       </c>
       <c r="C171" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D171" s="3">
-        <v>4.1474654377880185E-2</v>
+        <v>7.18232044198895E-2</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2789,13 +2789,13 @@
         <v>6</v>
       </c>
       <c r="B172" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C172" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D172" s="3">
-        <v>3.3519553072625698E-2</v>
+        <v>5.5401662049861494E-2</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2803,13 +2803,13 @@
         <v>6</v>
       </c>
       <c r="B173" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C173" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D173" s="3">
-        <v>4.6728971962616821E-2</v>
+        <v>4.1474654377880185E-2</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2820,10 +2820,10 @@
         <v>2022</v>
       </c>
       <c r="C174" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" s="3">
-        <v>6.1728395061728392E-2</v>
+        <v>3.3519553072625698E-2</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2834,10 +2834,10 @@
         <v>2022</v>
       </c>
       <c r="C175" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D175" s="3">
-        <v>7.116104868913857E-2</v>
+        <v>4.6728971962616821E-2</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2848,10 +2848,10 @@
         <v>2022</v>
       </c>
       <c r="C176" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D176" s="3">
-        <v>0.09</v>
+        <v>6.1728395061728392E-2</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2862,10 +2862,10 @@
         <v>2022</v>
       </c>
       <c r="C177" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D177" s="3">
-        <v>8.0939947780678853E-2</v>
+        <v>7.116104868913857E-2</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2876,10 +2876,10 @@
         <v>2022</v>
       </c>
       <c r="C178" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D178" s="3">
-        <v>6.3660477453580902E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2890,10 +2890,10 @@
         <v>2022</v>
       </c>
       <c r="C179" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D179" s="3">
-        <v>3.4482758620689655E-2</v>
+        <v>8.0939947780678853E-2</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2904,10 +2904,10 @@
         <v>2022</v>
       </c>
       <c r="C180" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D180" s="3">
-        <v>6.8870523415977963E-2</v>
+        <v>6.3660477453580902E-2</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2918,10 +2918,10 @@
         <v>2022</v>
       </c>
       <c r="C181" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D181" s="3">
-        <v>3.0769230769230771E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2932,10 +2932,10 @@
         <v>2022</v>
       </c>
       <c r="C182" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D182" s="3">
-        <v>4.6228710462287104E-2</v>
+        <v>6.8870523415977963E-2</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2946,10 +2946,10 @@
         <v>2022</v>
       </c>
       <c r="C183" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D183" s="3">
-        <v>6.1583577712609971E-2</v>
+        <v>3.0769230769230771E-2</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2957,13 +2957,13 @@
         <v>6</v>
       </c>
       <c r="B184" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C184" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D184" s="3">
-        <v>8.2508250825082508E-2</v>
+        <v>4.6228710462287104E-2</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2971,13 +2971,13 @@
         <v>6</v>
       </c>
       <c r="B185" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C185" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D185" s="3">
-        <v>6.6985645933014357E-2</v>
+        <v>6.1583577712609971E-2</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2988,10 +2988,10 @@
         <v>2023</v>
       </c>
       <c r="C186" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D186" s="3">
-        <v>5.3892215568862277E-2</v>
+        <v>8.2508250825082508E-2</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3002,10 +3002,10 @@
         <v>2023</v>
       </c>
       <c r="C187" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D187" s="3">
-        <v>3.0651340996168581E-2</v>
+        <v>6.6985645933014357E-2</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3016,10 +3016,10 @@
         <v>2023</v>
       </c>
       <c r="C188" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D188" s="3">
-        <v>6.798245614035088E-2</v>
+        <v>5.3892215568862277E-2</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3030,10 +3030,10 @@
         <v>2023</v>
       </c>
       <c r="C189" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D189" s="3">
-        <v>8.1012658227848103E-2</v>
+        <v>3.0651340996168581E-2</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3044,10 +3044,10 @@
         <v>2023</v>
       </c>
       <c r="C190" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D190" s="3">
-        <v>9.7995545657015584E-2</v>
+        <v>6.798245614035088E-2</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3058,10 +3058,10 @@
         <v>2023</v>
       </c>
       <c r="C191" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D191" s="3">
-        <v>7.0080862533692723E-2</v>
+        <v>8.1012658227848103E-2</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3072,10 +3072,10 @@
         <v>2023</v>
       </c>
       <c r="C192" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D192" s="3">
-        <v>8.9974293059125965E-2</v>
+        <v>9.7995545657015584E-2</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3086,10 +3086,10 @@
         <v>2023</v>
       </c>
       <c r="C193" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D193" s="3">
-        <v>8.3094555873925502E-2</v>
+        <v>7.0080862533692723E-2</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3100,10 +3100,10 @@
         <v>2023</v>
       </c>
       <c r="C194" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D194" s="3">
-        <v>7.2100313479623826E-2</v>
+        <v>8.9974293059125965E-2</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3114,10 +3114,10 @@
         <v>2023</v>
       </c>
       <c r="C195" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D195" s="3">
-        <v>6.3091482649842268E-2</v>
+        <v>8.3094555873925502E-2</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3125,13 +3125,13 @@
         <v>6</v>
       </c>
       <c r="B196" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C196" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D196" s="3">
-        <v>6.3897763578274758E-2</v>
+        <v>7.2100313479623826E-2</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3139,13 +3139,13 @@
         <v>6</v>
       </c>
       <c r="B197" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C197" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D197" s="3">
-        <v>6.4356435643564358E-2</v>
+        <v>6.3091482649842268E-2</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3156,10 +3156,10 @@
         <v>2024</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D198" s="3">
-        <v>5.4635761589403975E-2</v>
+        <v>6.3897763578274758E-2</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3170,10 +3170,10 @@
         <v>2024</v>
       </c>
       <c r="C199" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D199" s="3">
-        <v>7.3649754500818329E-2</v>
+        <v>6.4356435643564358E-2</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3184,10 +3184,10 @@
         <v>2024</v>
       </c>
       <c r="C200" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D200" s="3">
-        <v>6.0851926977687626E-2</v>
+        <v>5.4635761589403975E-2</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3198,10 +3198,10 @@
         <v>2024</v>
       </c>
       <c r="C201" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D201" s="3">
-        <v>5.2369077306733167E-2</v>
+        <v>7.3649754500818329E-2</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3212,10 +3212,10 @@
         <v>2024</v>
       </c>
       <c r="C202" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D202" s="3">
-        <v>7.7519379844961239E-2</v>
+        <v>6.0851926977687626E-2</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3226,10 +3226,10 @@
         <v>2024</v>
       </c>
       <c r="C203" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D203" s="3">
-        <v>8.0924855491329481E-2</v>
+        <v>5.2369077306733167E-2</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3240,10 +3240,10 @@
         <v>2024</v>
       </c>
       <c r="C204" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D204" s="3">
-        <v>9.585492227979274E-2</v>
+        <v>7.7519379844961239E-2</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3254,10 +3254,10 @@
         <v>2024</v>
       </c>
       <c r="C205" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D205" s="3">
-        <v>0.11811023622047244</v>
+        <v>8.0924855491329481E-2</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3268,10 +3268,10 @@
         <v>2024</v>
       </c>
       <c r="C206" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D206" s="3">
-        <v>9.9715099715099717E-2</v>
+        <v>9.585492227979274E-2</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3282,10 +3282,10 @@
         <v>2024</v>
       </c>
       <c r="C207" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D207" s="3">
-        <v>8.4158415841584164E-2</v>
+        <v>0.11811023622047244</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3293,13 +3293,13 @@
         <v>6</v>
       </c>
       <c r="B208" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C208" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D208" s="3">
-        <v>5.8139534883720929E-2</v>
+        <v>9.9715099715099717E-2</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3307,13 +3307,13 @@
         <v>6</v>
       </c>
       <c r="B209" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C209" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D209" s="3">
-        <v>4.6783625730994149E-2</v>
+        <v>8.4158415841584164E-2</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3324,10 +3324,10 @@
         <v>2025</v>
       </c>
       <c r="C210" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D210" s="3">
-        <v>3.6199095022624438E-2</v>
+        <v>5.8139534883720929E-2</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3338,10 +3338,10 @@
         <v>2025</v>
       </c>
       <c r="C211" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D211" s="3">
-        <v>4.2105263157894736E-2</v>
+        <v>4.6783625730994149E-2</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3352,10 +3352,10 @@
         <v>2025</v>
       </c>
       <c r="C212" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D212" s="3">
-        <v>3.925233644859813E-2</v>
+        <v>3.6199095022624438E-2</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3366,10 +3366,10 @@
         <v>2025</v>
       </c>
       <c r="C213" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D213" s="3">
-        <v>3.0905077262693158E-2</v>
+        <v>4.2105263157894736E-2</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3380,10 +3380,10 @@
         <v>2025</v>
       </c>
       <c r="C214" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D214" s="3">
-        <v>5.5555555555555552E-2</v>
+        <v>3.925233644859813E-2</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3394,10 +3394,10 @@
         <v>2025</v>
       </c>
       <c r="C215" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D215" s="3">
-        <v>4.4444444444444446E-2</v>
+        <v>3.0905077262693158E-2</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3408,10 +3408,10 @@
         <v>2025</v>
       </c>
       <c r="C216" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D216" s="3">
-        <v>3.678929765886288E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3422,10 +3422,10 @@
         <v>2025</v>
       </c>
       <c r="C217" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D217" s="3">
-        <v>7.6923076923076927E-2</v>
+        <v>4.4444444444444446E-2</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3436,10 +3436,10 @@
         <v>2025</v>
       </c>
       <c r="C218" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D218" s="3">
-        <v>4.2944785276073622E-2</v>
+        <v>3.678929765886288E-2</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3450,10 +3450,10 @@
         <v>2025</v>
       </c>
       <c r="C219" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D219" s="3">
-        <v>3.2835820895522387E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3461,13 +3461,13 @@
         <v>6</v>
       </c>
       <c r="B220" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C220" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D220" s="3">
-        <v>7.0671378091872794E-2</v>
+        <v>4.2944785276073622E-2</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3475,13 +3475,13 @@
         <v>6</v>
       </c>
       <c r="B221" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D221" s="3">
-        <v>3.7815126050420166E-2</v>
+        <v>3.273809523809524E-2</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3492,10 +3492,10 @@
         <v>2026</v>
       </c>
       <c r="C222" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" s="3">
-        <v>3.2258064516129031E-2</v>
+        <v>7.0671378091872794E-2</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3506,52 +3506,52 @@
         <v>2026</v>
       </c>
       <c r="C223" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D223" s="3">
-        <v>3.4602076124567475E-3</v>
+        <v>3.7815126050420166E-2</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B224" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C224" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224" s="3">
-        <v>3.5955056179775284E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B225" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C225" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D225" s="3">
-        <v>1.3392857142857142E-2</v>
+        <v>2.0618556701030927E-2</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B226" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C226" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D226" s="3">
-        <v>7.0754716981132077E-3</v>
+        <v>6.993006993006993E-3</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3562,10 +3562,10 @@
         <v>2020</v>
       </c>
       <c r="C227" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D227" s="3">
-        <v>2.0989505247376312E-2</v>
+        <v>3.5955056179775284E-2</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3576,10 +3576,10 @@
         <v>2020</v>
       </c>
       <c r="C228" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D228" s="3">
-        <v>2.828854314002829E-3</v>
+        <v>1.3392857142857142E-2</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3590,10 +3590,10 @@
         <v>2020</v>
       </c>
       <c r="C229" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D229" s="3">
-        <v>1.5015015015015015E-3</v>
+        <v>7.0754716981132077E-3</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3604,10 +3604,10 @@
         <v>2020</v>
       </c>
       <c r="C230" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D230" s="3">
-        <v>7.7760497667185074E-3</v>
+        <v>2.0989505247376312E-2</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3618,10 +3618,10 @@
         <v>2020</v>
       </c>
       <c r="C231" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D231" s="3">
-        <v>1.2797074954296161E-2</v>
+        <v>2.828854314002829E-3</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3632,10 +3632,10 @@
         <v>2020</v>
       </c>
       <c r="C232" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D232" s="3">
-        <v>1.7628205128205128E-2</v>
+        <v>1.5015015015015015E-3</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3646,10 +3646,10 @@
         <v>2020</v>
       </c>
       <c r="C233" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D233" s="3">
-        <v>2.1840873634945399E-2</v>
+        <v>7.7760497667185074E-3</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3660,10 +3660,10 @@
         <v>2020</v>
       </c>
       <c r="C234" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D234" s="3">
-        <v>1.282051282051282E-2</v>
+        <v>1.2797074954296161E-2</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3674,10 +3674,10 @@
         <v>2020</v>
       </c>
       <c r="C235" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D235" s="3">
-        <v>9.0361445783132526E-3</v>
+        <v>1.7628205128205128E-2</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3685,13 +3685,13 @@
         <v>7</v>
       </c>
       <c r="B236" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C236" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D236" s="3">
-        <v>2.800658978583196E-2</v>
+        <v>2.1840873634945399E-2</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3699,13 +3699,13 @@
         <v>7</v>
       </c>
       <c r="B237" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C237" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D237" s="3">
-        <v>1.384083044982699E-2</v>
+        <v>1.282051282051282E-2</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3713,13 +3713,13 @@
         <v>7</v>
       </c>
       <c r="B238" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C238" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D238" s="3">
-        <v>3.9630118890356669E-3</v>
+        <v>9.0361445783132526E-3</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3730,10 +3730,10 @@
         <v>2021</v>
       </c>
       <c r="C239" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D239" s="3">
-        <v>4.9833887043189366E-3</v>
+        <v>2.800658978583196E-2</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3744,10 +3744,10 @@
         <v>2021</v>
       </c>
       <c r="C240" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D240" s="3">
-        <v>8.291873963515755E-3</v>
+        <v>1.384083044982699E-2</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3758,10 +3758,10 @@
         <v>2021</v>
       </c>
       <c r="C241" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D241" s="3">
-        <v>6.4829821717990272E-3</v>
+        <v>3.9630118890356669E-3</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3772,10 +3772,10 @@
         <v>2021</v>
       </c>
       <c r="C242" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D242" s="3">
-        <v>1.3927576601671309E-2</v>
+        <v>4.9833887043189366E-3</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3786,10 +3786,10 @@
         <v>2021</v>
       </c>
       <c r="C243" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D243" s="3">
-        <v>1.3254786450662739E-2</v>
+        <v>8.291873963515755E-3</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3800,10 +3800,10 @@
         <v>2021</v>
       </c>
       <c r="C244" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D244" s="3">
-        <v>2.0872865275142316E-2</v>
+        <v>6.4829821717990272E-3</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3814,10 +3814,10 @@
         <v>2021</v>
       </c>
       <c r="C245" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D245" s="3">
-        <v>1.5432098765432098E-2</v>
+        <v>1.3927576601671309E-2</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3828,10 +3828,10 @@
         <v>2021</v>
       </c>
       <c r="C246" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D246" s="3">
-        <v>2.0900321543408359E-2</v>
+        <v>1.3254786450662739E-2</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3842,10 +3842,10 @@
         <v>2021</v>
       </c>
       <c r="C247" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D247" s="3">
-        <v>1.6344725111441308E-2</v>
+        <v>2.0872865275142316E-2</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3853,13 +3853,13 @@
         <v>7</v>
       </c>
       <c r="B248" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C248" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D248" s="3">
-        <v>7.5075075075075074E-3</v>
+        <v>1.5432098765432098E-2</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3867,13 +3867,13 @@
         <v>7</v>
       </c>
       <c r="B249" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C249" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D249" s="3">
-        <v>1.5238095238095238E-2</v>
+        <v>2.0900321543408359E-2</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3881,13 +3881,13 @@
         <v>7</v>
       </c>
       <c r="B250" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C250" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D250" s="3">
-        <v>2.6604068857589983E-2</v>
+        <v>1.6344725111441308E-2</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3898,10 +3898,10 @@
         <v>2022</v>
       </c>
       <c r="C251" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D251" s="3">
-        <v>3.8095238095238099E-2</v>
+        <v>7.5075075075075074E-3</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3912,10 +3912,10 @@
         <v>2022</v>
       </c>
       <c r="C252" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D252" s="3">
-        <v>1.238390092879257E-2</v>
+        <v>1.5238095238095238E-2</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3926,10 +3926,10 @@
         <v>2022</v>
       </c>
       <c r="C253" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D253" s="3">
-        <v>9.7719869706840382E-3</v>
+        <v>2.6604068857589983E-2</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3940,10 +3940,10 @@
         <v>2022</v>
       </c>
       <c r="C254" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D254" s="3">
-        <v>9.4191522762951327E-3</v>
+        <v>3.8095238095238099E-2</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3954,10 +3954,10 @@
         <v>2022</v>
       </c>
       <c r="C255" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D255" s="3">
-        <v>8.253094910591471E-3</v>
+        <v>1.238390092879257E-2</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3968,10 +3968,10 @@
         <v>2022</v>
       </c>
       <c r="C256" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D256" s="3">
-        <v>1.0230179028132993E-2</v>
+        <v>9.7719869706840382E-3</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3982,10 +3982,10 @@
         <v>2022</v>
       </c>
       <c r="C257" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D257" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>9.4191522762951327E-3</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3996,10 +3996,10 @@
         <v>2022</v>
       </c>
       <c r="C258" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D258" s="3">
-        <v>2.2091310751104567E-2</v>
+        <v>8.253094910591471E-3</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4010,10 +4010,10 @@
         <v>2022</v>
       </c>
       <c r="C259" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D259" s="3">
-        <v>2.5850340136054421E-2</v>
+        <v>1.0230179028132993E-2</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4021,13 +4021,13 @@
         <v>7</v>
       </c>
       <c r="B260" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C260" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D260" s="3">
-        <v>2.7656477438136828E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4035,13 +4035,13 @@
         <v>7</v>
       </c>
       <c r="B261" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C261" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D261" s="3">
-        <v>2.9957203994293864E-2</v>
+        <v>2.2091310751104567E-2</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4049,13 +4049,13 @@
         <v>7</v>
       </c>
       <c r="B262" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C262" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D262" s="3">
-        <v>3.7712895377128956E-2</v>
+        <v>2.5850340136054421E-2</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4066,10 +4066,10 @@
         <v>2023</v>
       </c>
       <c r="C263" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D263" s="3">
-        <v>4.3708609271523181E-2</v>
+        <v>2.7656477438136828E-2</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4080,10 +4080,10 @@
         <v>2023</v>
       </c>
       <c r="C264" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D264" s="3">
-        <v>2.1251475796930343E-2</v>
+        <v>2.9957203994293864E-2</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4094,10 +4094,10 @@
         <v>2023</v>
       </c>
       <c r="C265" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D265" s="3">
-        <v>2.7989821882951654E-2</v>
+        <v>3.7712895377128956E-2</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4108,10 +4108,10 @@
         <v>2023</v>
       </c>
       <c r="C266" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D266" s="3">
-        <v>2.442002442002442E-2</v>
+        <v>4.3708609271523181E-2</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4122,10 +4122,10 @@
         <v>2023</v>
       </c>
       <c r="C267" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D267" s="3">
-        <v>1.7488076311605722E-2</v>
+        <v>2.1251475796930343E-2</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4136,10 +4136,10 @@
         <v>2023</v>
       </c>
       <c r="C268" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D268" s="3">
-        <v>1.3924050632911392E-2</v>
+        <v>2.7989821882951654E-2</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4150,10 +4150,10 @@
         <v>2023</v>
       </c>
       <c r="C269" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D269" s="3">
-        <v>1.3615733736762481E-2</v>
+        <v>2.442002442002442E-2</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4164,10 +4164,10 @@
         <v>2023</v>
       </c>
       <c r="C270" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D270" s="3">
-        <v>2.3174971031286212E-2</v>
+        <v>1.7488076311605722E-2</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4178,10 +4178,10 @@
         <v>2023</v>
       </c>
       <c r="C271" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D271" s="3">
-        <v>2.7057497181510709E-2</v>
+        <v>1.3924050632911392E-2</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4189,13 +4189,13 @@
         <v>7</v>
       </c>
       <c r="B272" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C272" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D272" s="3">
-        <v>2.4608501118568233E-2</v>
+        <v>1.3615733736762481E-2</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4203,13 +4203,13 @@
         <v>7</v>
       </c>
       <c r="B273" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C273" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D273" s="3">
-        <v>3.9314516129032258E-2</v>
+        <v>2.3174971031286212E-2</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4217,13 +4217,13 @@
         <v>7</v>
       </c>
       <c r="B274" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C274" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D274" s="3">
-        <v>2.3907666941467436E-2</v>
+        <v>2.7057497181510709E-2</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4234,10 +4234,10 @@
         <v>2024</v>
       </c>
       <c r="C275" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D275" s="3">
-        <v>3.0755711775043937E-2</v>
+        <v>2.4608501118568233E-2</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4248,10 +4248,10 @@
         <v>2024</v>
       </c>
       <c r="C276" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D276" s="3">
-        <v>4.6968403074295471E-2</v>
+        <v>3.9314516129032258E-2</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4262,10 +4262,10 @@
         <v>2024</v>
       </c>
       <c r="C277" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D277" s="3">
-        <v>4.2056074766355138E-2</v>
+        <v>2.3907666941467436E-2</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4276,10 +4276,10 @@
         <v>2024</v>
       </c>
       <c r="C278" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D278" s="3">
-        <v>4.6168051708217916E-2</v>
+        <v>3.0755711775043937E-2</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4290,10 +4290,10 @@
         <v>2024</v>
       </c>
       <c r="C279" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D279" s="3">
-        <v>4.1121495327102804E-2</v>
+        <v>4.6968403074295471E-2</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4304,10 +4304,10 @@
         <v>2024</v>
       </c>
       <c r="C280" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D280" s="3">
-        <v>3.7401574803149609E-2</v>
+        <v>4.2056074766355138E-2</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4318,10 +4318,10 @@
         <v>2024</v>
       </c>
       <c r="C281" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D281" s="3">
-        <v>3.9413382218148489E-2</v>
+        <v>4.6168051708217916E-2</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4332,10 +4332,10 @@
         <v>2024</v>
       </c>
       <c r="C282" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D282" s="3">
-        <v>4.1666666666666664E-2</v>
+        <v>4.1121495327102804E-2</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4346,10 +4346,10 @@
         <v>2024</v>
       </c>
       <c r="C283" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D283" s="3">
-        <v>4.6095954844778929E-2</v>
+        <v>3.7401574803149609E-2</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4357,13 +4357,13 @@
         <v>7</v>
       </c>
       <c r="B284" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C284" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D284" s="3">
-        <v>4.363636363636364E-2</v>
+        <v>3.9413382218148489E-2</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4371,13 +4371,13 @@
         <v>7</v>
       </c>
       <c r="B285" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C285" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D285" s="3">
-        <v>3.536345776031434E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4385,13 +4385,13 @@
         <v>7</v>
       </c>
       <c r="B286" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C286" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D286" s="3">
-        <v>2.5129982668977469E-2</v>
+        <v>4.6095954844778929E-2</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4402,10 +4402,10 @@
         <v>2025</v>
       </c>
       <c r="C287" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D287" s="3">
-        <v>2.7372262773722629E-2</v>
+        <v>4.363636363636364E-2</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4416,10 +4416,10 @@
         <v>2025</v>
       </c>
       <c r="C288" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D288" s="3">
-        <v>1.1111111111111112E-2</v>
+        <v>3.536345776031434E-2</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4430,10 +4430,10 @@
         <v>2025</v>
       </c>
       <c r="C289" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D289" s="3">
-        <v>1.1737089201877934E-2</v>
+        <v>2.5129982668977469E-2</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4444,10 +4444,10 @@
         <v>2025</v>
       </c>
       <c r="C290" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D290" s="3">
-        <v>2.5089605734767026E-2</v>
+        <v>2.7397260273972601E-2</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4458,10 +4458,10 @@
         <v>2025</v>
       </c>
       <c r="C291" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D291" s="3">
-        <v>1.7992424242424244E-2</v>
+        <v>1.5170670037926675E-2</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4472,10 +4472,10 @@
         <v>2025</v>
       </c>
       <c r="C292" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D292" s="3">
-        <v>3.2579185520361993E-2</v>
+        <v>1.3669821240799159E-2</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4486,10 +4486,10 @@
         <v>2025</v>
       </c>
       <c r="C293" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D293" s="3">
-        <v>1.3409961685823755E-2</v>
+        <v>2.5089605734767026E-2</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4500,10 +4500,10 @@
         <v>2025</v>
       </c>
       <c r="C294" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D294" s="3">
-        <v>3.7298387096774195E-2</v>
+        <v>1.7992424242424244E-2</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4514,10 +4514,10 @@
         <v>2025</v>
       </c>
       <c r="C295" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D295" s="3">
-        <v>1.5957446808510637E-2</v>
+        <v>3.2579185520361993E-2</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4525,13 +4525,13 @@
         <v>7</v>
       </c>
       <c r="B296" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C296" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D296" s="3">
-        <v>1.0840108401084011E-2</v>
+        <v>1.3409961685823755E-2</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4539,13 +4539,13 @@
         <v>7</v>
       </c>
       <c r="B297" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C297" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D297" s="3">
-        <v>1.8450184501845018E-3</v>
+        <v>3.7298387096774195E-2</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4553,69 +4553,69 @@
         <v>7</v>
       </c>
       <c r="B298" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C298" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D298" s="3">
-        <v>2.9895366218236174E-3</v>
+        <v>1.5957446808510637E-2</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B299" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C299" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D299" s="3">
-        <v>6.7114093959731542E-3</v>
+        <v>1.0840108401084011E-2</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B300" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C300" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D300" s="3">
-        <v>7.3349633251833741E-3</v>
+        <v>2.7675276752767526E-3</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B301" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C301" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D301" s="3">
-        <v>5.681818181818182E-3</v>
+        <v>4.3478260869565218E-3</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B302" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C302" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D302" s="3">
-        <v>1.5677491601343786E-2</v>
+        <v>4.1841004184100415E-3</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4626,10 +4626,10 @@
         <v>2020</v>
       </c>
       <c r="C303" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D303" s="3">
-        <v>1.1142061281337047E-2</v>
+        <v>6.7114093959731542E-3</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4640,10 +4640,10 @@
         <v>2020</v>
       </c>
       <c r="C304" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D304" s="3">
-        <v>1.2154696132596685E-2</v>
+        <v>7.3349633251833741E-3</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4654,10 +4654,10 @@
         <v>2020</v>
       </c>
       <c r="C305" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D305" s="3">
-        <v>1.781970649895178E-2</v>
+        <v>5.681818181818182E-3</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4668,10 +4668,10 @@
         <v>2020</v>
       </c>
       <c r="C306" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D306" s="3">
-        <v>1.4705882352941176E-2</v>
+        <v>1.5677491601343786E-2</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4682,10 +4682,10 @@
         <v>2020</v>
       </c>
       <c r="C307" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D307" s="3">
-        <v>9.4936708860759497E-3</v>
+        <v>1.1142061281337047E-2</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4693,13 +4693,13 @@
         <v>8</v>
       </c>
       <c r="B308" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C308" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D308" s="3">
-        <v>3.6496350364963502E-3</v>
+        <v>1.2154696132596685E-2</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4707,13 +4707,13 @@
         <v>8</v>
       </c>
       <c r="B309" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C309" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D309" s="3">
-        <v>9.6463022508038593E-3</v>
+        <v>1.781970649895178E-2</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4721,13 +4721,13 @@
         <v>8</v>
       </c>
       <c r="B310" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C310" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D310" s="3">
-        <v>6.1349693251533744E-3</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4735,13 +4735,13 @@
         <v>8</v>
       </c>
       <c r="B311" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C311" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D311" s="3">
-        <v>2.7355623100303952E-2</v>
+        <v>9.4936708860759497E-3</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4752,10 +4752,10 @@
         <v>2021</v>
       </c>
       <c r="C312" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D312" s="3">
-        <v>1.3490725126475547E-2</v>
+        <v>3.6496350364963502E-3</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4766,10 +4766,10 @@
         <v>2021</v>
       </c>
       <c r="C313" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D313" s="3">
-        <v>1.425438596491228E-2</v>
+        <v>9.6463022508038593E-3</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4780,10 +4780,10 @@
         <v>2021</v>
       </c>
       <c r="C314" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D314" s="3">
-        <v>2.2754491017964073E-2</v>
+        <v>6.1349693251533744E-3</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4794,10 +4794,10 @@
         <v>2021</v>
       </c>
       <c r="C315" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D315" s="3">
-        <v>2.8037383177570093E-2</v>
+        <v>2.7355623100303952E-2</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4808,10 +4808,10 @@
         <v>2021</v>
       </c>
       <c r="C316" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D316" s="3">
-        <v>1.425438596491228E-2</v>
+        <v>1.3490725126475547E-2</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4822,10 +4822,10 @@
         <v>2021</v>
       </c>
       <c r="C317" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D317" s="3">
-        <v>2.3972602739726026E-2</v>
+        <v>1.425438596491228E-2</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4836,10 +4836,10 @@
         <v>2021</v>
       </c>
       <c r="C318" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D318" s="3">
-        <v>2.430939226519337E-2</v>
+        <v>2.2754491017964073E-2</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4847,13 +4847,13 @@
         <v>8</v>
       </c>
       <c r="B319" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C319" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D319" s="3">
-        <v>1.6797312430011199E-2</v>
+        <v>2.8037383177570093E-2</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4861,13 +4861,13 @@
         <v>8</v>
       </c>
       <c r="B320" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C320" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D320" s="3">
-        <v>3.0120481927710845E-3</v>
+        <v>1.425438596491228E-2</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4875,13 +4875,13 @@
         <v>8</v>
       </c>
       <c r="B321" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C321" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D321" s="3">
-        <v>1.1098779134295227E-2</v>
+        <v>2.3972602739726026E-2</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4889,13 +4889,13 @@
         <v>8</v>
       </c>
       <c r="B322" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C322" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D322" s="3">
-        <v>1.1574074074074073E-2</v>
+        <v>2.430939226519337E-2</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4906,10 +4906,10 @@
         <v>2022</v>
       </c>
       <c r="C323" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D323" s="3">
-        <v>1.5606242496998799E-2</v>
+        <v>1.6797312430011199E-2</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4920,10 +4920,10 @@
         <v>2022</v>
       </c>
       <c r="C324" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D324" s="3">
-        <v>1.8610421836228287E-2</v>
+        <v>3.0120481927710845E-3</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4934,10 +4934,10 @@
         <v>2022</v>
       </c>
       <c r="C325" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D325" s="3">
-        <v>1.8478260869565218E-2</v>
+        <v>1.1098779134295227E-2</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4948,10 +4948,10 @@
         <v>2022</v>
       </c>
       <c r="C326" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D326" s="3">
-        <v>1.913265306122449E-2</v>
+        <v>1.1574074074074073E-2</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4962,10 +4962,10 @@
         <v>2022</v>
       </c>
       <c r="C327" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D327" s="3">
-        <v>2.6315789473684209E-2</v>
+        <v>1.5606242496998799E-2</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4976,10 +4976,10 @@
         <v>2022</v>
       </c>
       <c r="C328" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D328" s="3">
-        <v>1.7492711370262391E-2</v>
+        <v>1.8610421836228287E-2</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4990,10 +4990,10 @@
         <v>2022</v>
       </c>
       <c r="C329" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D329" s="3">
-        <v>2.591283863368669E-2</v>
+        <v>1.8478260869565218E-2</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5004,10 +5004,10 @@
         <v>2022</v>
       </c>
       <c r="C330" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D330" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>1.913265306122449E-2</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5015,13 +5015,13 @@
         <v>8</v>
       </c>
       <c r="B331" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C331" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D331" s="3">
-        <v>1.8369690011481057E-2</v>
+        <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5029,13 +5029,13 @@
         <v>8</v>
       </c>
       <c r="B332" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C332" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D332" s="3">
-        <v>1.7456359102244388E-2</v>
+        <v>1.7492711370262391E-2</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5043,13 +5043,13 @@
         <v>8</v>
       </c>
       <c r="B333" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C333" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D333" s="3">
-        <v>1.627906976744186E-2</v>
+        <v>2.591283863368669E-2</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5057,13 +5057,13 @@
         <v>8</v>
       </c>
       <c r="B334" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C334" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D334" s="3">
-        <v>1.8518518518518517E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5074,10 +5074,10 @@
         <v>2023</v>
       </c>
       <c r="C335" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D335" s="3">
-        <v>2.0597322348094749E-2</v>
+        <v>1.8369690011481057E-2</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5088,10 +5088,10 @@
         <v>2023</v>
       </c>
       <c r="C336" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D336" s="3">
-        <v>2.0111731843575419E-2</v>
+        <v>1.7456359102244388E-2</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5102,10 +5102,10 @@
         <v>2023</v>
       </c>
       <c r="C337" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D337" s="3">
-        <v>2.5945945945945945E-2</v>
+        <v>1.627906976744186E-2</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5116,10 +5116,10 @@
         <v>2023</v>
       </c>
       <c r="C338" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D338" s="3">
-        <v>2.6709401709401708E-2</v>
+        <v>1.8518518518518517E-2</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5130,10 +5130,10 @@
         <v>2023</v>
       </c>
       <c r="C339" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D339" s="3">
-        <v>3.5087719298245612E-2</v>
+        <v>2.0597322348094749E-2</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5144,10 +5144,10 @@
         <v>2023</v>
       </c>
       <c r="C340" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D340" s="3">
-        <v>3.5460992907801421E-2</v>
+        <v>2.0111731843575419E-2</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5158,10 +5158,10 @@
         <v>2023</v>
       </c>
       <c r="C341" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D341" s="3">
-        <v>5.6928034371643392E-2</v>
+        <v>2.5945945945945945E-2</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5172,10 +5172,10 @@
         <v>2023</v>
       </c>
       <c r="C342" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D342" s="3">
-        <v>4.4979079497907949E-2</v>
+        <v>2.6709401709401708E-2</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5183,13 +5183,13 @@
         <v>8</v>
       </c>
       <c r="B343" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C343" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D343" s="3">
-        <v>3.7757437070938218E-2</v>
+        <v>3.5087719298245612E-2</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5197,13 +5197,13 @@
         <v>8</v>
       </c>
       <c r="B344" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C344" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D344" s="3">
-        <v>3.0092592592592591E-2</v>
+        <v>3.5460992907801421E-2</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5211,13 +5211,13 @@
         <v>8</v>
       </c>
       <c r="B345" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C345" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D345" s="3">
-        <v>2.9439696106362774E-2</v>
+        <v>5.6928034371643392E-2</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5225,13 +5225,13 @@
         <v>8</v>
       </c>
       <c r="B346" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C346" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D346" s="3">
-        <v>4.2074363992172209E-2</v>
+        <v>4.4979079497907949E-2</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5242,10 +5242,10 @@
         <v>2024</v>
       </c>
       <c r="C347" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D347" s="3">
-        <v>3.0274361400189215E-2</v>
+        <v>3.7757437070938218E-2</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5256,10 +5256,10 @@
         <v>2024</v>
       </c>
       <c r="C348" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D348" s="3">
-        <v>3.8014783526927137E-2</v>
+        <v>3.0092592592592591E-2</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5270,10 +5270,10 @@
         <v>2024</v>
       </c>
       <c r="C349" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D349" s="3">
-        <v>3.816046966731898E-2</v>
+        <v>2.9439696106362774E-2</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5284,10 +5284,10 @@
         <v>2024</v>
       </c>
       <c r="C350" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D350" s="3">
-        <v>2.3454157782515993E-2</v>
+        <v>4.2074363992172209E-2</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5298,10 +5298,10 @@
         <v>2024</v>
       </c>
       <c r="C351" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D351" s="3">
-        <v>2.3758099352051837E-2</v>
+        <v>3.0274361400189215E-2</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5312,10 +5312,10 @@
         <v>2024</v>
       </c>
       <c r="C352" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D352" s="3">
-        <v>2.6776519052523172E-2</v>
+        <v>3.8014783526927137E-2</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5326,10 +5326,10 @@
         <v>2024</v>
       </c>
       <c r="C353" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D353" s="3">
-        <v>3.2186459489456157E-2</v>
+        <v>3.816046966731898E-2</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5340,10 +5340,10 @@
         <v>2024</v>
       </c>
       <c r="C354" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D354" s="3">
-        <v>4.0363269424823413E-2</v>
+        <v>2.3454157782515993E-2</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5351,13 +5351,13 @@
         <v>8</v>
       </c>
       <c r="B355" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C355" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D355" s="3">
-        <v>2.0683453237410072E-2</v>
+        <v>2.3758099352051837E-2</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5365,13 +5365,13 @@
         <v>8</v>
       </c>
       <c r="B356" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C356" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D356" s="3">
-        <v>2.0942408376963352E-2</v>
+        <v>2.6776519052523172E-2</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5379,13 +5379,13 @@
         <v>8</v>
       </c>
       <c r="B357" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C357" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D357" s="3">
-        <v>3.0476190476190476E-2</v>
+        <v>3.2186459489456157E-2</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5393,13 +5393,13 @@
         <v>8</v>
       </c>
       <c r="B358" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C358" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D358" s="3">
-        <v>2.3255813953488372E-2</v>
+        <v>4.0363269424823413E-2</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5410,10 +5410,10 @@
         <v>2025</v>
       </c>
       <c r="C359" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D359" s="3">
-        <v>1.3774104683195593E-2</v>
+        <v>2.0683453237410072E-2</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5424,10 +5424,10 @@
         <v>2025</v>
       </c>
       <c r="C360" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D360" s="3">
-        <v>2.819548872180451E-2</v>
+        <v>2.0942408376963352E-2</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5438,10 +5438,10 @@
         <v>2025</v>
       </c>
       <c r="C361" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D361" s="3">
-        <v>1.4367816091954023E-2</v>
+        <v>3.0476190476190476E-2</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5452,10 +5452,10 @@
         <v>2025</v>
       </c>
       <c r="C362" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D362" s="3">
-        <v>1.8115942028985508E-2</v>
+        <v>2.3255813953488372E-2</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5466,10 +5466,10 @@
         <v>2025</v>
       </c>
       <c r="C363" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D363" s="3">
-        <v>2.133850630455868E-2</v>
+        <v>1.3774104683195593E-2</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5480,10 +5480,10 @@
         <v>2025</v>
       </c>
       <c r="C364" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D364" s="3">
-        <v>1.7346053772766695E-2</v>
+        <v>2.819548872180451E-2</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5494,10 +5494,10 @@
         <v>2025</v>
       </c>
       <c r="C365" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D365" s="3">
-        <v>2.3429179978700747E-2</v>
+        <v>1.4367816091954023E-2</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5508,10 +5508,10 @@
         <v>2025</v>
       </c>
       <c r="C366" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D366" s="3">
-        <v>1.2206572769953052E-2</v>
+        <v>1.8115942028985508E-2</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5519,13 +5519,13 @@
         <v>8</v>
       </c>
       <c r="B367" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C367" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D367" s="3">
-        <v>1.3171225937183385E-2</v>
+        <v>2.133850630455868E-2</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5533,13 +5533,13 @@
         <v>8</v>
       </c>
       <c r="B368" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C368" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D368" s="3">
-        <v>7.82122905027933E-3</v>
+        <v>1.7361111111111112E-2</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5547,13 +5547,13 @@
         <v>8</v>
       </c>
       <c r="B369" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C369" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D369" s="3">
-        <v>1.1235955056179775E-2</v>
+        <v>2.3429179978700747E-2</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5561,83 +5561,83 @@
         <v>8</v>
       </c>
       <c r="B370" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C370" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D370" s="3">
-        <v>1.9337016574585635E-2</v>
+        <v>1.2206572769953052E-2</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B371" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C371" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D371" s="3">
-        <v>8.5470085470085479E-3</v>
+        <v>1.3171225937183385E-2</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B372" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C372" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3">
-        <v>1.7811704834605598E-2</v>
+        <v>7.82122905027933E-3</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B373" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C373" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D373" s="3">
-        <v>1.9197207678883072E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B374" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C374" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D374" s="3">
-        <v>4.307116104868914E-2</v>
+        <v>3.8461538461538464E-2</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B375" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C375" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D375" s="3">
-        <v>4.96031746031746E-2</v>
+        <v>9.202453987730062E-3</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5648,10 +5648,10 @@
         <v>2019</v>
       </c>
       <c r="C376" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D376" s="3">
-        <v>3.5714285714285712E-2</v>
+        <v>8.5470085470085479E-3</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5662,10 +5662,10 @@
         <v>2019</v>
       </c>
       <c r="C377" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D377" s="3">
-        <v>6.4202334630350189E-2</v>
+        <v>1.7811704834605598E-2</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5676,10 +5676,10 @@
         <v>2019</v>
       </c>
       <c r="C378" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D378" s="3">
-        <v>3.6458333333333336E-2</v>
+        <v>1.9197207678883072E-2</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5687,13 +5687,13 @@
         <v>9</v>
       </c>
       <c r="B379" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C379" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D379" s="3">
-        <v>2.1848739495798318E-2</v>
+        <v>4.307116104868914E-2</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5701,13 +5701,13 @@
         <v>9</v>
       </c>
       <c r="B380" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C380" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D380" s="3">
-        <v>4.0336134453781515E-2</v>
+        <v>4.96031746031746E-2</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5715,13 +5715,13 @@
         <v>9</v>
       </c>
       <c r="B381" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C381" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D381" s="3">
-        <v>3.5200000000000002E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5729,13 +5729,13 @@
         <v>9</v>
       </c>
       <c r="B382" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C382" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D382" s="3">
-        <v>4.3029259896729774E-2</v>
+        <v>6.4202334630350189E-2</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5743,13 +5743,13 @@
         <v>9</v>
       </c>
       <c r="B383" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C383" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D383" s="3">
-        <v>5.6603773584905662E-2</v>
+        <v>3.6458333333333336E-2</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5760,10 +5760,10 @@
         <v>2020</v>
       </c>
       <c r="C384" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D384" s="3">
-        <v>5.6910569105691054E-2</v>
+        <v>2.1848739495798318E-2</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5774,10 +5774,10 @@
         <v>2020</v>
       </c>
       <c r="C385" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D385" s="3">
-        <v>5.2953156822810592E-2</v>
+        <v>4.0336134453781515E-2</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5788,10 +5788,10 @@
         <v>2020</v>
       </c>
       <c r="C386" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D386" s="3">
-        <v>5.4393305439330547E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5802,10 +5802,10 @@
         <v>2020</v>
       </c>
       <c r="C387" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D387" s="3">
-        <v>5.8585858585858588E-2</v>
+        <v>4.3029259896729774E-2</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5816,10 +5816,10 @@
         <v>2020</v>
       </c>
       <c r="C388" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D388" s="3">
-        <v>4.6747967479674794E-2</v>
+        <v>5.6603773584905662E-2</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5830,10 +5830,10 @@
         <v>2020</v>
       </c>
       <c r="C389" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D389" s="3">
-        <v>5.2083333333333336E-2</v>
+        <v>5.6910569105691054E-2</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5844,10 +5844,10 @@
         <v>2020</v>
       </c>
       <c r="C390" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D390" s="3">
-        <v>8.3333333333333329E-2</v>
+        <v>5.2953156822810592E-2</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5855,13 +5855,13 @@
         <v>9</v>
       </c>
       <c r="B391" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C391" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D391" s="3">
-        <v>3.8535645472061654E-2</v>
+        <v>5.4393305439330547E-2</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5869,13 +5869,13 @@
         <v>9</v>
       </c>
       <c r="B392" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C392" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D392" s="3">
-        <v>2.7726432532347505E-2</v>
+        <v>5.8585858585858588E-2</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5883,13 +5883,13 @@
         <v>9</v>
       </c>
       <c r="B393" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C393" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D393" s="3">
-        <v>4.5375218150087257E-2</v>
+        <v>4.6747967479674794E-2</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5897,13 +5897,13 @@
         <v>9</v>
       </c>
       <c r="B394" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C394" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D394" s="3">
-        <v>4.7463175122749592E-2</v>
+        <v>5.2083333333333336E-2</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5911,13 +5911,13 @@
         <v>9</v>
       </c>
       <c r="B395" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C395" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D395" s="3">
-        <v>4.0219378427787937E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5928,10 +5928,10 @@
         <v>2021</v>
       </c>
       <c r="C396" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D396" s="3">
-        <v>3.8181818181818185E-2</v>
+        <v>3.8535645472061654E-2</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5942,10 +5942,10 @@
         <v>2021</v>
       </c>
       <c r="C397" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D397" s="3">
-        <v>3.5825545171339561E-2</v>
+        <v>2.7726432532347505E-2</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5956,10 +5956,10 @@
         <v>2021</v>
       </c>
       <c r="C398" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D398" s="3">
-        <v>2.7210884353741496E-2</v>
+        <v>4.5375218150087257E-2</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5970,10 +5970,10 @@
         <v>2021</v>
       </c>
       <c r="C399" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D399" s="3">
-        <v>3.8142620232172471E-2</v>
+        <v>4.7463175122749592E-2</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -5984,10 +5984,10 @@
         <v>2021</v>
       </c>
       <c r="C400" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D400" s="3">
-        <v>3.041144901610018E-2</v>
+        <v>4.0219378427787937E-2</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -5998,10 +5998,10 @@
         <v>2021</v>
       </c>
       <c r="C401" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D401" s="3">
-        <v>3.4071550255536626E-2</v>
+        <v>3.8181818181818185E-2</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6012,10 +6012,10 @@
         <v>2021</v>
       </c>
       <c r="C402" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D402" s="3">
-        <v>2.5210084033613446E-2</v>
+        <v>3.5825545171339561E-2</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6023,13 +6023,13 @@
         <v>9</v>
       </c>
       <c r="B403" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C403" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D403" s="3">
-        <v>2.5454545454545455E-2</v>
+        <v>2.7210884353741496E-2</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6037,13 +6037,13 @@
         <v>9</v>
       </c>
       <c r="B404" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C404" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D404" s="3">
-        <v>3.5523978685612786E-2</v>
+        <v>3.8142620232172471E-2</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6051,13 +6051,13 @@
         <v>9</v>
       </c>
       <c r="B405" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C405" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D405" s="3">
-        <v>2.9411764705882353E-2</v>
+        <v>3.041144901610018E-2</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6065,13 +6065,13 @@
         <v>9</v>
       </c>
       <c r="B406" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C406" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D406" s="3">
-        <v>2.6604068857589983E-2</v>
+        <v>3.4071550255536626E-2</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6079,13 +6079,13 @@
         <v>9</v>
       </c>
       <c r="B407" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C407" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D407" s="3">
-        <v>3.6163522012578615E-2</v>
+        <v>2.5210084033613446E-2</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6096,10 +6096,10 @@
         <v>2022</v>
       </c>
       <c r="C408" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D408" s="3">
-        <v>4.0584415584415584E-2</v>
+        <v>2.5454545454545455E-2</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6110,10 +6110,10 @@
         <v>2022</v>
       </c>
       <c r="C409" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D409" s="3">
-        <v>3.2786885245901641E-2</v>
+        <v>3.5523978685612786E-2</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6124,10 +6124,10 @@
         <v>2022</v>
       </c>
       <c r="C410" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D410" s="3">
-        <v>3.7096774193548385E-2</v>
+        <v>2.9411764705882353E-2</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6138,10 +6138,10 @@
         <v>2022</v>
       </c>
       <c r="C411" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D411" s="3">
-        <v>4.716981132075472E-2</v>
+        <v>2.6604068857589983E-2</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6152,10 +6152,10 @@
         <v>2022</v>
       </c>
       <c r="C412" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D412" s="3">
-        <v>3.3457249070631967E-2</v>
+        <v>3.6163522012578615E-2</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6166,10 +6166,10 @@
         <v>2022</v>
       </c>
       <c r="C413" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D413" s="3">
-        <v>3.6912751677852351E-2</v>
+        <v>4.0584415584415584E-2</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6180,10 +6180,10 @@
         <v>2022</v>
       </c>
       <c r="C414" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D414" s="3">
-        <v>2.6711185308848081E-2</v>
+        <v>3.2786885245901641E-2</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6191,13 +6191,13 @@
         <v>9</v>
       </c>
       <c r="B415" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C415" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D415" s="3">
-        <v>3.1914893617021274E-2</v>
+        <v>3.7096774193548385E-2</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6205,13 +6205,13 @@
         <v>9</v>
       </c>
       <c r="B416" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C416" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D416" s="3">
-        <v>1.9064124783362217E-2</v>
+        <v>4.716981132075472E-2</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6219,13 +6219,13 @@
         <v>9</v>
       </c>
       <c r="B417" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C417" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D417" s="3">
-        <v>3.2400589101620032E-2</v>
+        <v>3.3457249070631967E-2</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6233,13 +6233,13 @@
         <v>9</v>
       </c>
       <c r="B418" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C418" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D418" s="3">
-        <v>2.1739130434782608E-2</v>
+        <v>3.6912751677852351E-2</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6247,13 +6247,13 @@
         <v>9</v>
       </c>
       <c r="B419" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C419" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D419" s="3">
-        <v>2.923076923076923E-2</v>
+        <v>2.6711185308848081E-2</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6264,10 +6264,10 @@
         <v>2023</v>
       </c>
       <c r="C420" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D420" s="3">
-        <v>2.0437956204379562E-2</v>
+        <v>3.1914893617021274E-2</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6278,10 +6278,10 @@
         <v>2023</v>
       </c>
       <c r="C421" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D421" s="3">
-        <v>2.5723472668810289E-2</v>
+        <v>1.9064124783362217E-2</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6292,10 +6292,10 @@
         <v>2023</v>
       </c>
       <c r="C422" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D422" s="3">
-        <v>2.2968197879858657E-2</v>
+        <v>3.2400589101620032E-2</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6306,10 +6306,10 @@
         <v>2023</v>
       </c>
       <c r="C423" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D423" s="3">
-        <v>3.39943342776204E-2</v>
+        <v>2.1739130434782608E-2</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6320,10 +6320,10 @@
         <v>2023</v>
       </c>
       <c r="C424" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D424" s="3">
-        <v>1.7391304347826087E-2</v>
+        <v>2.923076923076923E-2</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6334,10 +6334,10 @@
         <v>2023</v>
       </c>
       <c r="C425" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D425" s="3">
-        <v>4.2483660130718956E-2</v>
+        <v>2.0437956204379562E-2</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6348,10 +6348,10 @@
         <v>2023</v>
       </c>
       <c r="C426" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D426" s="3">
-        <v>3.5561877667140827E-2</v>
+        <v>2.5723472668810289E-2</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6359,13 +6359,13 @@
         <v>9</v>
       </c>
       <c r="B427" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C427" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D427" s="3">
-        <v>2.5974025974025976E-2</v>
+        <v>2.2968197879858657E-2</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6373,13 +6373,13 @@
         <v>9</v>
       </c>
       <c r="B428" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C428" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D428" s="3">
-        <v>2.823920265780731E-2</v>
+        <v>3.39943342776204E-2</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6387,13 +6387,13 @@
         <v>9</v>
       </c>
       <c r="B429" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C429" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D429" s="3">
-        <v>1.2949640287769784E-2</v>
+        <v>1.7391304347826087E-2</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6401,13 +6401,13 @@
         <v>9</v>
       </c>
       <c r="B430" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C430" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D430" s="3">
-        <v>1.5673981191222569E-2</v>
+        <v>4.2483660130718956E-2</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6415,13 +6415,13 @@
         <v>9</v>
       </c>
       <c r="B431" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C431" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D431" s="3">
-        <v>2.8106508875739646E-2</v>
+        <v>3.5561877667140827E-2</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6432,10 +6432,10 @@
         <v>2024</v>
       </c>
       <c r="C432" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D432" s="3">
-        <v>2.4844720496894408E-2</v>
+        <v>2.5974025974025976E-2</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6446,10 +6446,10 @@
         <v>2024</v>
       </c>
       <c r="C433" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D433" s="3">
-        <v>4.4478527607361963E-2</v>
+        <v>2.823920265780731E-2</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6460,10 +6460,10 @@
         <v>2024</v>
       </c>
       <c r="C434" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D434" s="3">
-        <v>2.6912181303116147E-2</v>
+        <v>1.2949640287769784E-2</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6474,10 +6474,10 @@
         <v>2024</v>
       </c>
       <c r="C435" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D435" s="3">
-        <v>3.3236994219653176E-2</v>
+        <v>1.5673981191222569E-2</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6488,10 +6488,10 @@
         <v>2024</v>
       </c>
       <c r="C436" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D436" s="3">
-        <v>3.287671232876712E-2</v>
+        <v>2.8106508875739646E-2</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6502,10 +6502,10 @@
         <v>2024</v>
       </c>
       <c r="C437" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D437" s="3">
-        <v>1.849217638691323E-2</v>
+        <v>2.4844720496894408E-2</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6516,10 +6516,10 @@
         <v>2024</v>
       </c>
       <c r="C438" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D438" s="3">
-        <v>2.0270270270270271E-2</v>
+        <v>4.4478527607361963E-2</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6527,13 +6527,13 @@
         <v>9</v>
       </c>
       <c r="B439" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C439" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D439" s="3">
-        <v>2.3809523809523808E-2</v>
+        <v>2.6912181303116147E-2</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6541,13 +6541,13 @@
         <v>9</v>
       </c>
       <c r="B440" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C440" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D440" s="3">
-        <v>1.6742770167427701E-2</v>
+        <v>3.3236994219653176E-2</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6555,13 +6555,13 @@
         <v>9</v>
       </c>
       <c r="B441" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C441" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D441" s="3">
-        <v>2.9891304347826088E-2</v>
+        <v>3.287671232876712E-2</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6569,13 +6569,13 @@
         <v>9</v>
       </c>
       <c r="B442" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C442" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D442" s="3">
-        <v>4.9019607843137254E-2</v>
+        <v>1.849217638691323E-2</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6583,13 +6583,13 @@
         <v>9</v>
       </c>
       <c r="B443" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C443" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D443" s="3">
-        <v>3.1157270029673591E-2</v>
+        <v>2.0270270270270271E-2</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6600,10 +6600,10 @@
         <v>2025</v>
       </c>
       <c r="C444" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D444" s="3">
-        <v>1.9858156028368795E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6614,10 +6614,10 @@
         <v>2025</v>
       </c>
       <c r="C445" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D445" s="3">
-        <v>1.0810810810810811E-2</v>
+        <v>1.6742770167427701E-2</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6628,10 +6628,10 @@
         <v>2025</v>
       </c>
       <c r="C446" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D446" s="3">
-        <v>1.2640449438202247E-2</v>
+        <v>2.9891304347826088E-2</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6642,10 +6642,10 @@
         <v>2025</v>
       </c>
       <c r="C447" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D447" s="3">
-        <v>1.2391573729863693E-2</v>
+        <v>4.9019607843137254E-2</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6656,10 +6656,10 @@
         <v>2025</v>
       </c>
       <c r="C448" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D448" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>3.1157270029673591E-2</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6670,10 +6670,10 @@
         <v>2025</v>
       </c>
       <c r="C449" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D449" s="3">
-        <v>7.8125E-3</v>
+        <v>1.9858156028368795E-2</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6684,10 +6684,10 @@
         <v>2025</v>
       </c>
       <c r="C450" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D450" s="3">
-        <v>6.7842605156037995E-3</v>
+        <v>1.0810810810810811E-2</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6695,13 +6695,13 @@
         <v>9</v>
       </c>
       <c r="B451" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C451" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D451" s="3">
-        <v>1.2484394506866416E-2</v>
+        <v>1.2640449438202247E-2</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6709,13 +6709,13 @@
         <v>9</v>
       </c>
       <c r="B452" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C452" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D452" s="3">
-        <v>2.8530670470756064E-3</v>
+        <v>1.2391573729863693E-2</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6723,13 +6723,13 @@
         <v>9</v>
       </c>
       <c r="B453" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C453" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D453" s="3">
-        <v>1.1538461538461539E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6737,97 +6737,97 @@
         <v>9</v>
       </c>
       <c r="B454" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C454" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D454" s="3">
-        <v>3.8610038610038611E-3</v>
+        <v>7.8125E-3</v>
       </c>
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B455" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C455" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D455" s="3">
-        <v>1.9801980198019802E-2</v>
+        <v>6.7842605156037995E-3</v>
       </c>
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B456" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C456" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D456" s="3">
-        <v>1</v>
+        <v>1.2484394506866416E-2</v>
       </c>
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B457" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C457" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D457" s="3">
-        <v>4.878048780487805E-2</v>
+        <v>2.8530670470756064E-3</v>
       </c>
     </row>
     <row r="458" spans="1:4">
       <c r="A458" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B458" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C458" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D458" s="3">
-        <v>2.030456852791878E-2</v>
+        <v>1.1538461538461539E-2</v>
       </c>
     </row>
     <row r="459" spans="1:4">
       <c r="A459" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B459" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C459" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D459" s="3">
-        <v>3.6842105263157891E-2</v>
+        <v>3.8610038610038611E-3</v>
       </c>
     </row>
     <row r="460" spans="1:4">
       <c r="A460" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B460" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C460" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D460" s="3">
-        <v>2.7777777777777776E-2</v>
+        <v>5.1993067590987872E-3</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6835,13 +6835,13 @@
         <v>10</v>
       </c>
       <c r="B461" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C461" s="2">
         <v>10</v>
       </c>
       <c r="D461" s="3">
-        <v>5.5214723926380369E-2</v>
+        <v>1.9801980198019802E-2</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6852,10 +6852,10 @@
         <v>2020</v>
       </c>
       <c r="C462" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D462" s="3">
-        <v>4.0540540540540543E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6866,10 +6866,10 @@
         <v>2020</v>
       </c>
       <c r="C463" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D463" s="3">
-        <v>1.935483870967742E-2</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6877,13 +6877,13 @@
         <v>10</v>
       </c>
       <c r="B464" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C464" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D464" s="3">
-        <v>3.4482758620689655E-2</v>
+        <v>2.030456852791878E-2</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6891,13 +6891,13 @@
         <v>10</v>
       </c>
       <c r="B465" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C465" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D465" s="3">
-        <v>2.7972027972027972E-2</v>
+        <v>3.6842105263157891E-2</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6905,13 +6905,13 @@
         <v>10</v>
       </c>
       <c r="B466" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C466" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D466" s="3">
-        <v>3.5294117647058823E-2</v>
+        <v>2.7777777777777776E-2</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6919,13 +6919,13 @@
         <v>10</v>
       </c>
       <c r="B467" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C467" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D467" s="3">
-        <v>2.8571428571428571E-2</v>
+        <v>5.5214723926380369E-2</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6933,13 +6933,13 @@
         <v>10</v>
       </c>
       <c r="B468" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C468" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D468" s="3">
-        <v>1.1049723756906077E-2</v>
+        <v>4.0540540540540543E-2</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6947,13 +6947,13 @@
         <v>10</v>
       </c>
       <c r="B469" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C469" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D469" s="3">
-        <v>3.8674033149171269E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6964,10 +6964,10 @@
         <v>2021</v>
       </c>
       <c r="C470" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D470" s="3">
-        <v>6.3157894736842107E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6978,10 +6978,10 @@
         <v>2021</v>
       </c>
       <c r="C471" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D471" s="3">
-        <v>3.4090909090909088E-2</v>
+        <v>2.7972027972027972E-2</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6992,10 +6992,10 @@
         <v>2021</v>
       </c>
       <c r="C472" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D472" s="3">
-        <v>3.7735849056603772E-2</v>
+        <v>3.5294117647058823E-2</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7006,10 +7006,10 @@
         <v>2021</v>
       </c>
       <c r="C473" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D473" s="3">
-        <v>4.1916167664670656E-2</v>
+        <v>2.8571428571428571E-2</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7020,10 +7020,10 @@
         <v>2021</v>
       </c>
       <c r="C474" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D474" s="3">
-        <v>3.5175879396984924E-2</v>
+        <v>1.1049723756906077E-2</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7034,10 +7034,10 @@
         <v>2021</v>
       </c>
       <c r="C475" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D475" s="3">
-        <v>6.2857142857142861E-2</v>
+        <v>3.8674033149171269E-2</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7045,13 +7045,13 @@
         <v>10</v>
       </c>
       <c r="B476" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C476" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D476" s="3">
-        <v>2.1917808219178082E-2</v>
+        <v>6.3157894736842107E-2</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7059,13 +7059,13 @@
         <v>10</v>
       </c>
       <c r="B477" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C477" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D477" s="3">
-        <v>2.9239766081871343E-2</v>
+        <v>3.4090909090909088E-2</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7073,13 +7073,13 @@
         <v>10</v>
       </c>
       <c r="B478" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C478" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D478" s="3">
-        <v>4.1095890410958902E-2</v>
+        <v>3.7735849056603772E-2</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7087,13 +7087,13 @@
         <v>10</v>
       </c>
       <c r="B479" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C479" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D479" s="3">
-        <v>6.2893081761006293E-3</v>
+        <v>4.1916167664670656E-2</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7101,13 +7101,13 @@
         <v>10</v>
       </c>
       <c r="B480" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C480" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D480" s="3">
-        <v>2.0270270270270271E-2</v>
+        <v>3.5175879396984924E-2</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7115,13 +7115,13 @@
         <v>10</v>
       </c>
       <c r="B481" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C481" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D481" s="3">
-        <v>2.5773195876288658E-2</v>
+        <v>6.2857142857142861E-2</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7132,10 +7132,10 @@
         <v>2022</v>
       </c>
       <c r="C482" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D482" s="3">
-        <v>3.7634408602150539E-2</v>
+        <v>2.1917808219178082E-2</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7146,10 +7146,10 @@
         <v>2022</v>
       </c>
       <c r="C483" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D483" s="3">
-        <v>2.247191011235955E-2</v>
+        <v>2.9239766081871343E-2</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7160,10 +7160,10 @@
         <v>2022</v>
       </c>
       <c r="C484" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D484" s="3">
-        <v>3.0120481927710843E-2</v>
+        <v>4.1095890410958902E-2</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7174,10 +7174,10 @@
         <v>2022</v>
       </c>
       <c r="C485" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D485" s="3">
-        <v>1.3422818791946308E-2</v>
+        <v>6.2893081761006293E-3</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7188,10 +7188,10 @@
         <v>2022</v>
       </c>
       <c r="C486" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D486" s="3">
-        <v>2.2857142857142857E-2</v>
+        <v>2.0270270270270271E-2</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7199,13 +7199,13 @@
         <v>10</v>
       </c>
       <c r="B487" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C487" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D487" s="3">
-        <v>3.9325842696629212E-2</v>
+        <v>2.5773195876288658E-2</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7213,13 +7213,13 @@
         <v>10</v>
       </c>
       <c r="B488" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C488" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D488" s="3">
-        <v>1.9607843137254902E-2</v>
+        <v>3.7634408602150539E-2</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7227,13 +7227,13 @@
         <v>10</v>
       </c>
       <c r="B489" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C489" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D489" s="3">
-        <v>3.3112582781456956E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7241,13 +7241,13 @@
         <v>10</v>
       </c>
       <c r="B490" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C490" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D490" s="3">
-        <v>2.247191011235955E-2</v>
+        <v>3.0120481927710843E-2</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7255,13 +7255,13 @@
         <v>10</v>
       </c>
       <c r="B491" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C491" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D491" s="3">
-        <v>3.0864197530864196E-2</v>
+        <v>1.3422818791946308E-2</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7269,13 +7269,13 @@
         <v>10</v>
       </c>
       <c r="B492" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C492" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D492" s="3">
-        <v>4.3956043956043959E-2</v>
+        <v>2.2857142857142857E-2</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7286,10 +7286,10 @@
         <v>2023</v>
       </c>
       <c r="C493" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D493" s="3">
-        <v>3.5714285714285712E-2</v>
+        <v>3.9325842696629212E-2</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7300,10 +7300,10 @@
         <v>2023</v>
       </c>
       <c r="C494" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D494" s="3">
-        <v>0.04</v>
+        <v>1.9607843137254902E-2</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7314,10 +7314,10 @@
         <v>2023</v>
       </c>
       <c r="C495" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D495" s="3">
-        <v>2.2598870056497175E-2</v>
+        <v>3.3112582781456956E-2</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7328,10 +7328,10 @@
         <v>2023</v>
       </c>
       <c r="C496" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D496" s="3">
-        <v>3.0864197530864196E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7342,10 +7342,10 @@
         <v>2023</v>
       </c>
       <c r="C497" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D497" s="3">
-        <v>7.3529411764705885E-2</v>
+        <v>3.0864197530864196E-2</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7356,10 +7356,10 @@
         <v>2023</v>
       </c>
       <c r="C498" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D498" s="3">
-        <v>2.4875621890547265E-2</v>
+        <v>4.3956043956043959E-2</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7367,13 +7367,13 @@
         <v>10</v>
       </c>
       <c r="B499" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C499" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D499" s="3">
-        <v>2.2522522522522521E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7381,13 +7381,13 @@
         <v>10</v>
       </c>
       <c r="B500" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C500" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D500" s="3">
-        <v>3.1413612565445025E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7395,13 +7395,13 @@
         <v>10</v>
       </c>
       <c r="B501" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C501" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D501" s="3">
-        <v>3.6649214659685861E-2</v>
+        <v>2.2598870056497175E-2</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7409,13 +7409,13 @@
         <v>10</v>
       </c>
       <c r="B502" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C502" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D502" s="3">
-        <v>2.6178010471204188E-2</v>
+        <v>3.0864197530864196E-2</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7423,13 +7423,13 @@
         <v>10</v>
       </c>
       <c r="B503" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C503" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D503" s="3">
-        <v>3.9408866995073892E-2</v>
+        <v>7.3529411764705885E-2</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7437,13 +7437,13 @@
         <v>10</v>
       </c>
       <c r="B504" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C504" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D504" s="3">
-        <v>1.2195121951219513E-2</v>
+        <v>2.4875621890547265E-2</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7454,10 +7454,10 @@
         <v>2024</v>
       </c>
       <c r="C505" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D505" s="3">
-        <v>6.2500000000000003E-3</v>
+        <v>2.2522522522522521E-2</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7468,10 +7468,10 @@
         <v>2024</v>
       </c>
       <c r="C506" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D506" s="3">
-        <v>5.3191489361702126E-3</v>
+        <v>3.1413612565445025E-2</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7482,10 +7482,10 @@
         <v>2024</v>
       </c>
       <c r="C507" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D507" s="3">
-        <v>1.1627906976744186E-2</v>
+        <v>3.6649214659685861E-2</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7496,10 +7496,10 @@
         <v>2024</v>
       </c>
       <c r="C508" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D508" s="3">
-        <v>3.9215686274509803E-3</v>
+        <v>2.6178010471204188E-2</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7507,13 +7507,13 @@
         <v>10</v>
       </c>
       <c r="B509" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C509" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D509" s="3">
-        <v>1.1857707509881422E-2</v>
+        <v>3.9408866995073892E-2</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7521,13 +7521,13 @@
         <v>10</v>
       </c>
       <c r="B510" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C510" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D510" s="3">
-        <v>4.1322314049586778E-3</v>
+        <v>1.2195121951219513E-2</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7535,13 +7535,13 @@
         <v>10</v>
       </c>
       <c r="B511" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C511" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D511" s="3">
-        <v>4.0650406504065045E-3</v>
+        <v>6.2500000000000003E-3</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7549,13 +7549,13 @@
         <v>10</v>
       </c>
       <c r="B512" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C512" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D512" s="3">
-        <v>4.1666666666666666E-3</v>
+        <v>5.3191489361702126E-3</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7563,13 +7563,13 @@
         <v>10</v>
       </c>
       <c r="B513" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C513" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D513" s="3">
-        <v>3.787878787878788E-3</v>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -7577,13 +7577,13 @@
         <v>10</v>
       </c>
       <c r="B514" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C514" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D514" s="3">
-        <v>8.2644628099173556E-3</v>
+        <v>3.9215686274509803E-3</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7594,10 +7594,10 @@
         <v>2025</v>
       </c>
       <c r="C515" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D515" s="3">
-        <v>4.464285714285714E-3</v>
+        <v>1.1857707509881422E-2</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7608,10 +7608,10 @@
         <v>2025</v>
       </c>
       <c r="C516" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D516" s="3">
-        <v>4.8780487804878049E-3</v>
+        <v>4.1322314049586778E-3</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7619,13 +7619,13 @@
         <v>10</v>
       </c>
       <c r="B517" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C517" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D517" s="3">
-        <v>1.1764705882352941E-2</v>
+        <v>4.0650406504065045E-3</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7633,111 +7633,111 @@
         <v>10</v>
       </c>
       <c r="B518" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C518" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D518" s="3">
-        <v>8.0321285140562242E-3</v>
+        <v>4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B519" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C519" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D519" s="3">
-        <v>7.4257425742574254E-3</v>
+        <v>3.787878787878788E-3</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B520" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C520" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D520" s="3">
-        <v>7.6335877862595417E-3</v>
+        <v>8.2644628099173556E-3</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B521" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C521" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D521" s="3">
-        <v>1.2987012987012988E-2</v>
+        <v>4.464285714285714E-3</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B522" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="C522" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D522" s="3">
-        <v>2.2388059701492536E-2</v>
+        <v>4.8780487804878049E-3</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B523" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C523" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D523" s="3">
-        <v>9.74025974025974E-3</v>
+        <v>1.1764705882352941E-2</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B524" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C524" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D524" s="3">
-        <v>1.1267605633802818E-2</v>
+        <v>8.0321285140562242E-3</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B525" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C525" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D525" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>5.7142857142857143E-3</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7748,10 +7748,10 @@
         <v>2020</v>
       </c>
       <c r="C526" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D526" s="3">
-        <v>1.7291066282420751E-2</v>
+        <v>7.4257425742574254E-3</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7762,10 +7762,10 @@
         <v>2020</v>
       </c>
       <c r="C527" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D527" s="3">
-        <v>1.65016501650165E-2</v>
+        <v>7.6335877862595417E-3</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7776,10 +7776,10 @@
         <v>2020</v>
       </c>
       <c r="C528" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D528" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>1.2987012987012988E-2</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7790,10 +7790,10 @@
         <v>2020</v>
       </c>
       <c r="C529" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D529" s="3">
-        <v>1.3745704467353952E-2</v>
+        <v>2.2388059701492536E-2</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7801,13 +7801,13 @@
         <v>11</v>
       </c>
       <c r="B530" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C530" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D530" s="3">
-        <v>1.11731843575419E-2</v>
+        <v>9.74025974025974E-3</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7815,13 +7815,13 @@
         <v>11</v>
       </c>
       <c r="B531" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C531" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D531" s="3">
-        <v>7.6335877862595417E-3</v>
+        <v>1.1267605633802818E-2</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7829,13 +7829,13 @@
         <v>11</v>
       </c>
       <c r="B532" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C532" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D532" s="3">
-        <v>2.8301886792452831E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7843,13 +7843,13 @@
         <v>11</v>
       </c>
       <c r="B533" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C533" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D533" s="3">
-        <v>1.1933174224343675E-2</v>
+        <v>1.7291066282420751E-2</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7857,13 +7857,13 @@
         <v>11</v>
       </c>
       <c r="B534" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C534" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D534" s="3">
-        <v>5.5096418732782371E-3</v>
+        <v>1.65016501650165E-2</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7871,13 +7871,13 @@
         <v>11</v>
       </c>
       <c r="B535" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C535" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D535" s="3">
-        <v>1.2048192771084338E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7885,13 +7885,13 @@
         <v>11</v>
       </c>
       <c r="B536" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C536" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D536" s="3">
-        <v>1.5290519877675841E-2</v>
+        <v>1.3745704467353952E-2</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7902,10 +7902,10 @@
         <v>2021</v>
       </c>
       <c r="C537" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D537" s="3">
-        <v>5.6497175141242938E-3</v>
+        <v>1.11731843575419E-2</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7916,10 +7916,10 @@
         <v>2021</v>
       </c>
       <c r="C538" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D538" s="3">
-        <v>1.2269938650306749E-2</v>
+        <v>7.6335877862595417E-3</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7930,10 +7930,10 @@
         <v>2021</v>
       </c>
       <c r="C539" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D539" s="3">
-        <v>1.7543859649122806E-2</v>
+        <v>2.8301886792452831E-2</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7944,10 +7944,10 @@
         <v>2021</v>
       </c>
       <c r="C540" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D540" s="3">
-        <v>2.4464831804281346E-2</v>
+        <v>1.1933174224343675E-2</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7958,10 +7958,10 @@
         <v>2021</v>
       </c>
       <c r="C541" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D541" s="3">
-        <v>1.5544041450777202E-2</v>
+        <v>5.5096418732782371E-3</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7969,13 +7969,13 @@
         <v>11</v>
       </c>
       <c r="B542" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C542" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D542" s="3">
-        <v>7.6142131979695434E-3</v>
+        <v>1.2048192771084338E-2</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7983,13 +7983,13 @@
         <v>11</v>
       </c>
       <c r="B543" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C543" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D543" s="3">
-        <v>1.1049723756906077E-2</v>
+        <v>1.5290519877675841E-2</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -7997,13 +7997,13 @@
         <v>11</v>
       </c>
       <c r="B544" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C544" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D544" s="3">
-        <v>1.912568306010929E-2</v>
+        <v>5.6497175141242938E-3</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8011,13 +8011,13 @@
         <v>11</v>
       </c>
       <c r="B545" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C545" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D545" s="3">
-        <v>1.9021739130434784E-2</v>
+        <v>1.2269938650306749E-2</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8025,13 +8025,13 @@
         <v>11</v>
       </c>
       <c r="B546" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C546" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D546" s="3">
-        <v>1.8421052631578946E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8039,13 +8039,13 @@
         <v>11</v>
       </c>
       <c r="B547" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C547" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D547" s="3">
-        <v>2.9508196721311476E-2</v>
+        <v>2.4464831804281346E-2</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8053,13 +8053,13 @@
         <v>11</v>
       </c>
       <c r="B548" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C548" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D548" s="3">
-        <v>2.3809523809523808E-2</v>
+        <v>1.5544041450777202E-2</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8070,10 +8070,10 @@
         <v>2022</v>
       </c>
       <c r="C549" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D549" s="3">
-        <v>1.2562814070351759E-2</v>
+        <v>7.6142131979695434E-3</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8084,10 +8084,10 @@
         <v>2022</v>
       </c>
       <c r="C550" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D550" s="3">
-        <v>1.2106537530266344E-2</v>
+        <v>1.1049723756906077E-2</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8098,10 +8098,10 @@
         <v>2022</v>
       </c>
       <c r="C551" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D551" s="3">
-        <v>1.6085790884718499E-2</v>
+        <v>1.912568306010929E-2</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8112,10 +8112,10 @@
         <v>2022</v>
       </c>
       <c r="C552" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D552" s="3">
-        <v>7.9787234042553185E-3</v>
+        <v>1.9021739130434784E-2</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8126,10 +8126,10 @@
         <v>2022</v>
       </c>
       <c r="C553" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D553" s="3">
-        <v>3.0959752321981426E-3</v>
+        <v>1.8421052631578946E-2</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8137,13 +8137,13 @@
         <v>11</v>
       </c>
       <c r="B554" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C554" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D554" s="3">
-        <v>5.8651026392961877E-3</v>
+        <v>2.9508196721311476E-2</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8151,13 +8151,13 @@
         <v>11</v>
       </c>
       <c r="B555" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C555" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D555" s="3">
-        <v>1.9498607242339833E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8165,13 +8165,13 @@
         <v>11</v>
       </c>
       <c r="B556" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C556" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D556" s="3">
-        <v>9.852216748768473E-3</v>
+        <v>1.2562814070351759E-2</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8179,13 +8179,13 @@
         <v>11</v>
       </c>
       <c r="B557" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C557" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D557" s="3">
-        <v>2.0833333333333332E-2</v>
+        <v>1.2106537530266344E-2</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8193,13 +8193,13 @@
         <v>11</v>
       </c>
       <c r="B558" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C558" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D558" s="3">
-        <v>2.3419203747072601E-2</v>
+        <v>1.6085790884718499E-2</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8207,13 +8207,13 @@
         <v>11</v>
       </c>
       <c r="B559" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C559" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D559" s="3">
-        <v>1.8181818181818181E-2</v>
+        <v>7.9787234042553185E-3</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8221,13 +8221,13 @@
         <v>11</v>
       </c>
       <c r="B560" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C560" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D560" s="3">
-        <v>1.5151515151515152E-2</v>
+        <v>3.0959752321981426E-3</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8238,10 +8238,10 @@
         <v>2023</v>
       </c>
       <c r="C561" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D561" s="3">
-        <v>2.1028037383177569E-2</v>
+        <v>5.8651026392961877E-3</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8252,10 +8252,10 @@
         <v>2023</v>
       </c>
       <c r="C562" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D562" s="3">
-        <v>2.6128266033254157E-2</v>
+        <v>1.9498607242339833E-2</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8266,10 +8266,10 @@
         <v>2023</v>
       </c>
       <c r="C563" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D563" s="3">
-        <v>1.1600928074245939E-2</v>
+        <v>9.852216748768473E-3</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8280,10 +8280,10 @@
         <v>2023</v>
       </c>
       <c r="C564" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D564" s="3">
-        <v>1.3698630136986301E-2</v>
+        <v>2.0833333333333332E-2</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8294,10 +8294,10 @@
         <v>2023</v>
       </c>
       <c r="C565" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D565" s="3">
-        <v>2.4330900243309004E-2</v>
+        <v>2.3419203747072601E-2</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8305,13 +8305,13 @@
         <v>11</v>
       </c>
       <c r="B566" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C566" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D566" s="3">
-        <v>0.02</v>
+        <v>1.8181818181818181E-2</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8319,13 +8319,13 @@
         <v>11</v>
       </c>
       <c r="B567" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C567" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D567" s="3">
-        <v>3.1630170316301706E-2</v>
+        <v>1.5151515151515152E-2</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8333,13 +8333,13 @@
         <v>11</v>
       </c>
       <c r="B568" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C568" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D568" s="3">
-        <v>2.9473684210526315E-2</v>
+        <v>2.1028037383177569E-2</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8347,13 +8347,13 @@
         <v>11</v>
       </c>
       <c r="B569" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C569" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D569" s="3">
-        <v>1.4981273408239701E-2</v>
+        <v>2.6128266033254157E-2</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8361,13 +8361,13 @@
         <v>11</v>
       </c>
       <c r="B570" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C570" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D570" s="3">
-        <v>2.1568627450980392E-2</v>
+        <v>1.1600928074245939E-2</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8375,13 +8375,13 @@
         <v>11</v>
       </c>
       <c r="B571" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C571" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D571" s="3">
-        <v>1.2474012474012475E-2</v>
+        <v>1.3698630136986301E-2</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8389,13 +8389,13 @@
         <v>11</v>
       </c>
       <c r="B572" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C572" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D572" s="3">
-        <v>2.9279279279279279E-2</v>
+        <v>2.4330900243309004E-2</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8406,10 +8406,10 @@
         <v>2024</v>
       </c>
       <c r="C573" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D573" s="3">
-        <v>1.8518518518518517E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8420,10 +8420,10 @@
         <v>2024</v>
       </c>
       <c r="C574" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D574" s="3">
-        <v>2.0661157024793389E-2</v>
+        <v>3.1630170316301706E-2</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8434,10 +8434,10 @@
         <v>2024</v>
       </c>
       <c r="C575" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D575" s="3">
-        <v>2.7472527472527472E-2</v>
+        <v>2.9473684210526315E-2</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8448,10 +8448,10 @@
         <v>2024</v>
       </c>
       <c r="C576" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D576" s="3">
-        <v>1.3245033112582781E-2</v>
+        <v>1.4981273408239701E-2</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8462,10 +8462,10 @@
         <v>2024</v>
       </c>
       <c r="C577" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D577" s="3">
-        <v>1.4251781472684086E-2</v>
+        <v>2.1568627450980392E-2</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8473,13 +8473,13 @@
         <v>11</v>
       </c>
       <c r="B578" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C578" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D578" s="3">
-        <v>1.8957345971563982E-2</v>
+        <v>1.2474012474012475E-2</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8487,13 +8487,13 @@
         <v>11</v>
       </c>
       <c r="B579" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C579" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D579" s="3">
-        <v>1.8099547511312219E-2</v>
+        <v>2.9279279279279279E-2</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8501,13 +8501,13 @@
         <v>11</v>
       </c>
       <c r="B580" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C580" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D580" s="3">
-        <v>3.5650623885918001E-3</v>
+        <v>1.8518518518518517E-2</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8515,13 +8515,13 @@
         <v>11</v>
       </c>
       <c r="B581" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C581" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D581" s="3">
-        <v>3.616636528028933E-3</v>
+        <v>2.0661157024793389E-2</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8529,13 +8529,13 @@
         <v>11</v>
       </c>
       <c r="B582" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C582" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D582" s="3">
-        <v>3.3333333333333335E-3</v>
+        <v>2.7472527472527472E-2</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8543,13 +8543,13 @@
         <v>11</v>
       </c>
       <c r="B583" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C583" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D583" s="3">
-        <v>1.8621973929236499E-3</v>
+        <v>1.3245033112582781E-2</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8557,13 +8557,13 @@
         <v>11</v>
       </c>
       <c r="B584" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C584" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D584" s="3">
-        <v>5.5762081784386614E-3</v>
+        <v>1.4251781472684086E-2</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8574,10 +8574,10 @@
         <v>2025</v>
       </c>
       <c r="C585" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D585" s="3">
-        <v>1.3565891472868217E-2</v>
+        <v>1.8957345971563982E-2</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -8588,10 +8588,10 @@
         <v>2025</v>
       </c>
       <c r="C586" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D586" s="3">
-        <v>5.4644808743169399E-3</v>
+        <v>1.8099547511312219E-2</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -8602,10 +8602,10 @@
         <v>2025</v>
       </c>
       <c r="C587" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D587" s="3">
-        <v>5.905511811023622E-3</v>
+        <v>3.5650623885918001E-3</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -8616,10 +8616,10 @@
         <v>2025</v>
       </c>
       <c r="C588" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D588" s="3">
-        <v>6.1099796334012219E-3</v>
+        <v>3.616636528028933E-3</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8627,13 +8627,13 @@
         <v>11</v>
       </c>
       <c r="B589" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C589" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D589" s="3">
-        <v>1.3544018058690745E-2</v>
+        <v>3.3333333333333335E-3</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -8641,13 +8641,13 @@
         <v>11</v>
       </c>
       <c r="B590" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C590" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D590" s="3">
-        <v>6.3157894736842104E-3</v>
+        <v>1.8621973929236499E-3</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8655,111 +8655,111 @@
         <v>11</v>
       </c>
       <c r="B591" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C591" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D591" s="3">
-        <v>2.1141649048625794E-3</v>
+        <v>5.5762081784386614E-3</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B592" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C592" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D592" s="3">
-        <v>6.024096385542169E-3</v>
+        <v>1.3565891472868217E-2</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B593" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C593" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D593" s="3">
-        <v>1.2750455373406194E-2</v>
+        <v>5.4644808743169399E-3</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B594" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C594" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D594" s="3">
-        <v>5.1679586563307496E-3</v>
+        <v>5.905511811023622E-3</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B595" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C595" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D595" s="3">
-        <v>8.6830680173661367E-3</v>
+        <v>6.1099796334012219E-3</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B596" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C596" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D596" s="3">
-        <v>1.1661807580174927E-2</v>
+        <v>1.3544018058690745E-2</v>
       </c>
     </row>
     <row r="597" spans="1:4">
       <c r="A597" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B597" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C597" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D597" s="3">
-        <v>6.2305295950155761E-3</v>
+        <v>6.3157894736842104E-3</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B598" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C598" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D598" s="3">
-        <v>1.466275659824047E-2</v>
+        <v>6.2111801242236021E-3</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8767,13 +8767,13 @@
         <v>12</v>
       </c>
       <c r="B599" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C599" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D599" s="3">
-        <v>3.5714285714285713E-3</v>
+        <v>6.024096385542169E-3</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8781,13 +8781,13 @@
         <v>12</v>
       </c>
       <c r="B600" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C600" s="2">
         <v>9</v>
       </c>
       <c r="D600" s="3">
-        <v>6.8143100511073255E-3</v>
+        <v>1.2750455373406194E-2</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8795,13 +8795,13 @@
         <v>12</v>
       </c>
       <c r="B601" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C601" s="2">
         <v>10</v>
       </c>
       <c r="D601" s="3">
-        <v>7.4074074074074077E-3</v>
+        <v>5.1679586563307496E-3</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8809,13 +8809,13 @@
         <v>12</v>
       </c>
       <c r="B602" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C602" s="2">
         <v>11</v>
       </c>
       <c r="D602" s="3">
-        <v>1.437699680511182E-2</v>
+        <v>8.6830680173661367E-3</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8823,13 +8823,13 @@
         <v>12</v>
       </c>
       <c r="B603" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C603" s="2">
         <v>12</v>
       </c>
       <c r="D603" s="3">
-        <v>1.002004008016032E-2</v>
+        <v>1.1661807580174927E-2</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8837,13 +8837,13 @@
         <v>12</v>
       </c>
       <c r="B604" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C604" s="2">
         <v>1</v>
       </c>
       <c r="D604" s="3">
-        <v>1.751592356687898E-2</v>
+        <v>6.2305295950155761E-3</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8851,13 +8851,13 @@
         <v>12</v>
       </c>
       <c r="B605" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C605" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D605" s="3">
-        <v>4.807692307692308E-3</v>
+        <v>1.466275659824047E-2</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8865,13 +8865,13 @@
         <v>12</v>
       </c>
       <c r="B606" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C606" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D606" s="3">
-        <v>7.3529411764705881E-3</v>
+        <v>3.5714285714285713E-3</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8879,13 +8879,13 @@
         <v>12</v>
       </c>
       <c r="B607" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C607" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D607" s="3">
-        <v>1.3235294117647059E-2</v>
+        <v>6.8143100511073255E-3</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8893,13 +8893,13 @@
         <v>12</v>
       </c>
       <c r="B608" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C608" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D608" s="3">
-        <v>1.1283497884344146E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8907,13 +8907,13 @@
         <v>12</v>
       </c>
       <c r="B609" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C609" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D609" s="3">
-        <v>8.8757396449704144E-3</v>
+        <v>1.437699680511182E-2</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8921,13 +8921,13 @@
         <v>12</v>
       </c>
       <c r="B610" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C610" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D610" s="3">
-        <v>8.9020771513353119E-3</v>
+        <v>1.002004008016032E-2</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8938,10 +8938,10 @@
         <v>2021</v>
       </c>
       <c r="C611" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D611" s="3">
-        <v>9.3833780160857902E-3</v>
+        <v>1.751592356687898E-2</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8952,10 +8952,10 @@
         <v>2021</v>
       </c>
       <c r="C612" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D612" s="3">
-        <v>7.462686567164179E-3</v>
+        <v>4.807692307692308E-3</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8966,10 +8966,10 @@
         <v>2021</v>
       </c>
       <c r="C613" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D613" s="3">
-        <v>5.008347245409015E-3</v>
+        <v>7.3529411764705881E-3</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8980,10 +8980,10 @@
         <v>2021</v>
       </c>
       <c r="C614" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D614" s="3">
-        <v>1.9969278033794162E-2</v>
+        <v>1.3235294117647059E-2</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8994,10 +8994,10 @@
         <v>2021</v>
       </c>
       <c r="C615" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D615" s="3">
-        <v>1.3953488372093023E-2</v>
+        <v>1.1283497884344146E-2</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9005,13 +9005,13 @@
         <v>12</v>
       </c>
       <c r="B616" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C616" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D616" s="3">
-        <v>1.8867924528301886E-2</v>
+        <v>8.8757396449704144E-3</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9019,13 +9019,13 @@
         <v>12</v>
       </c>
       <c r="B617" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C617" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D617" s="3">
-        <v>1.7241379310344827E-2</v>
+        <v>8.9020771513353119E-3</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9033,13 +9033,13 @@
         <v>12</v>
       </c>
       <c r="B618" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C618" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D618" s="3">
-        <v>1.7725258493353029E-2</v>
+        <v>9.3833780160857902E-3</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9047,13 +9047,13 @@
         <v>12</v>
       </c>
       <c r="B619" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C619" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D619" s="3">
-        <v>5.1020408163265302E-3</v>
+        <v>7.462686567164179E-3</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9061,13 +9061,13 @@
         <v>12</v>
       </c>
       <c r="B620" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C620" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D620" s="3">
-        <v>1.3157894736842105E-2</v>
+        <v>5.008347245409015E-3</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9075,13 +9075,13 @@
         <v>12</v>
       </c>
       <c r="B621" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C621" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D621" s="3">
-        <v>1.5015015015015015E-2</v>
+        <v>1.9969278033794162E-2</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9089,13 +9089,13 @@
         <v>12</v>
       </c>
       <c r="B622" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C622" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D622" s="3">
-        <v>2.0558002936857563E-2</v>
+        <v>1.3953488372093023E-2</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9106,10 +9106,10 @@
         <v>2022</v>
       </c>
       <c r="C623" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D623" s="3">
-        <v>1.2965964343598054E-2</v>
+        <v>1.8867924528301886E-2</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9120,10 +9120,10 @@
         <v>2022</v>
       </c>
       <c r="C624" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D624" s="3">
-        <v>1.7828200972447326E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9134,10 +9134,10 @@
         <v>2022</v>
       </c>
       <c r="C625" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D625" s="3">
-        <v>2.1885521885521887E-2</v>
+        <v>1.7725258493353029E-2</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9148,10 +9148,10 @@
         <v>2022</v>
       </c>
       <c r="C626" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D626" s="3">
-        <v>1.2965964343598054E-2</v>
+        <v>5.1020408163265302E-3</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9162,10 +9162,10 @@
         <v>2022</v>
       </c>
       <c r="C627" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D627" s="3">
-        <v>1.6296296296296295E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9173,13 +9173,13 @@
         <v>12</v>
       </c>
       <c r="B628" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C628" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D628" s="3">
-        <v>1.3910355486862442E-2</v>
+        <v>1.5015015015015015E-2</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9187,13 +9187,13 @@
         <v>12</v>
       </c>
       <c r="B629" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C629" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D629" s="3">
-        <v>1.4516129032258065E-2</v>
+        <v>2.0558002936857563E-2</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9201,13 +9201,13 @@
         <v>12</v>
       </c>
       <c r="B630" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C630" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D630" s="3">
-        <v>1.9920318725099601E-2</v>
+        <v>1.2965964343598054E-2</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9215,13 +9215,13 @@
         <v>12</v>
       </c>
       <c r="B631" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C631" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D631" s="3">
-        <v>1.2213740458015267E-2</v>
+        <v>1.7828200972447326E-2</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9229,13 +9229,13 @@
         <v>12</v>
       </c>
       <c r="B632" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C632" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D632" s="3">
-        <v>1.8018018018018018E-2</v>
+        <v>2.1885521885521887E-2</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9243,13 +9243,13 @@
         <v>12</v>
       </c>
       <c r="B633" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C633" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D633" s="3">
-        <v>2.0689655172413793E-2</v>
+        <v>1.2965964343598054E-2</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9257,13 +9257,13 @@
         <v>12</v>
       </c>
       <c r="B634" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C634" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D634" s="3">
-        <v>1.4598540145985401E-2</v>
+        <v>1.6296296296296295E-2</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9274,10 +9274,10 @@
         <v>2023</v>
       </c>
       <c r="C635" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D635" s="3">
-        <v>1.9886363636363636E-2</v>
+        <v>1.3910355486862442E-2</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9288,10 +9288,10 @@
         <v>2023</v>
       </c>
       <c r="C636" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D636" s="3">
-        <v>1.9345238095238096E-2</v>
+        <v>1.4516129032258065E-2</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9302,10 +9302,10 @@
         <v>2023</v>
       </c>
       <c r="C637" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D637" s="3">
-        <v>2.5920873124147339E-2</v>
+        <v>1.9920318725099601E-2</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9316,10 +9316,10 @@
         <v>2023</v>
       </c>
       <c r="C638" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D638" s="3">
-        <v>2.4011299435028249E-2</v>
+        <v>1.2213740458015267E-2</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9330,10 +9330,10 @@
         <v>2023</v>
       </c>
       <c r="C639" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D639" s="3">
-        <v>2.2818791946308724E-2</v>
+        <v>1.8018018018018018E-2</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9341,13 +9341,13 @@
         <v>12</v>
       </c>
       <c r="B640" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C640" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D640" s="3">
-        <v>1.7804154302670624E-2</v>
+        <v>2.0689655172413793E-2</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9355,13 +9355,13 @@
         <v>12</v>
       </c>
       <c r="B641" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C641" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D641" s="3">
-        <v>1.2569832402234637E-2</v>
+        <v>1.4598540145985401E-2</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9369,13 +9369,13 @@
         <v>12</v>
       </c>
       <c r="B642" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C642" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D642" s="3">
-        <v>2.564102564102564E-2</v>
+        <v>1.9886363636363636E-2</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9383,13 +9383,13 @@
         <v>12</v>
       </c>
       <c r="B643" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C643" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D643" s="3">
-        <v>2.7027027027027029E-2</v>
+        <v>1.9345238095238096E-2</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9397,13 +9397,13 @@
         <v>12</v>
       </c>
       <c r="B644" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C644" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D644" s="3">
-        <v>2.0915032679738561E-2</v>
+        <v>2.5920873124147339E-2</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9411,13 +9411,13 @@
         <v>12</v>
       </c>
       <c r="B645" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C645" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D645" s="3">
-        <v>2.3952095808383235E-2</v>
+        <v>2.4011299435028249E-2</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9425,13 +9425,13 @@
         <v>12</v>
       </c>
       <c r="B646" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C646" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D646" s="3">
-        <v>2.1551724137931036E-2</v>
+        <v>2.2818791946308724E-2</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9442,10 +9442,10 @@
         <v>2024</v>
       </c>
       <c r="C647" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D647" s="3">
-        <v>2.6315789473684209E-2</v>
+        <v>1.7804154302670624E-2</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9456,10 +9456,10 @@
         <v>2024</v>
       </c>
       <c r="C648" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D648" s="3">
-        <v>9.2592592592592587E-3</v>
+        <v>1.2569832402234637E-2</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9470,10 +9470,10 @@
         <v>2024</v>
       </c>
       <c r="C649" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D649" s="3">
-        <v>7.7279752704791345E-3</v>
+        <v>2.564102564102564E-2</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9484,10 +9484,10 @@
         <v>2024</v>
       </c>
       <c r="C650" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D650" s="3">
-        <v>6.5359477124183009E-3</v>
+        <v>2.7027027027027029E-2</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9498,10 +9498,10 @@
         <v>2024</v>
       </c>
       <c r="C651" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D651" s="3">
-        <v>1.0835913312693499E-2</v>
+        <v>2.0915032679738561E-2</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9509,13 +9509,13 @@
         <v>12</v>
       </c>
       <c r="B652" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C652" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D652" s="3">
-        <v>7.3099415204678359E-3</v>
+        <v>2.3952095808383235E-2</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9523,13 +9523,13 @@
         <v>12</v>
       </c>
       <c r="B653" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C653" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D653" s="3">
-        <v>1.0852713178294573E-2</v>
+        <v>2.1551724137931036E-2</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9537,13 +9537,13 @@
         <v>12</v>
       </c>
       <c r="B654" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C654" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D654" s="3">
-        <v>6.2893081761006293E-3</v>
+        <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9551,13 +9551,13 @@
         <v>12</v>
       </c>
       <c r="B655" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C655" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D655" s="3">
-        <v>7.7821011673151752E-3</v>
+        <v>9.2592592592592587E-3</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9565,13 +9565,13 @@
         <v>12</v>
       </c>
       <c r="B656" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C656" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D656" s="3">
-        <v>2.4330900243309003E-3</v>
+        <v>7.7279752704791345E-3</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -9579,13 +9579,13 @@
         <v>12</v>
       </c>
       <c r="B657" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C657" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D657" s="3">
-        <v>6.6844919786096255E-3</v>
+        <v>6.5359477124183009E-3</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -9593,13 +9593,13 @@
         <v>12</v>
       </c>
       <c r="B658" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C658" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D658" s="3">
-        <v>3.0769230769230769E-3</v>
+        <v>1.0835913312693499E-2</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -9610,10 +9610,10 @@
         <v>2025</v>
       </c>
       <c r="C659" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D659" s="3">
-        <v>5.6497175141242938E-3</v>
+        <v>7.3099415204678359E-3</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -9624,10 +9624,10 @@
         <v>2025</v>
       </c>
       <c r="C660" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D660" s="3">
-        <v>1.1283497884344146E-2</v>
+        <v>1.0852713178294573E-2</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -9638,10 +9638,10 @@
         <v>2025</v>
       </c>
       <c r="C661" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D661" s="3">
-        <v>8.658008658008658E-3</v>
+        <v>6.2893081761006293E-3</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -9652,10 +9652,10 @@
         <v>2025</v>
       </c>
       <c r="C662" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D662" s="3">
-        <v>8.5106382978723406E-3</v>
+        <v>7.7821011673151752E-3</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -9663,13 +9663,13 @@
         <v>12</v>
       </c>
       <c r="B663" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C663" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D663" s="3">
-        <v>2.8050490883590462E-3</v>
+        <v>2.4330900243309003E-3</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -9677,13 +9677,13 @@
         <v>12</v>
       </c>
       <c r="B664" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C664" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D664" s="3">
-        <v>1.4306151645207439E-3</v>
+        <v>6.6844919786096255E-3</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -9691,13 +9691,125 @@
         <v>12</v>
       </c>
       <c r="B665" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C665" s="2">
+        <v>8</v>
+      </c>
+      <c r="D665" s="3">
+        <v>3.0769230769230769E-3</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4">
+      <c r="A666" t="s">
+        <v>12</v>
+      </c>
+      <c r="B666" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C666" s="2">
+        <v>9</v>
+      </c>
+      <c r="D666" s="3">
+        <v>5.6497175141242938E-3</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4">
+      <c r="A667" t="s">
+        <v>12</v>
+      </c>
+      <c r="B667" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C667" s="2">
+        <v>10</v>
+      </c>
+      <c r="D667" s="3">
+        <v>1.1283497884344146E-2</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4">
+      <c r="A668" t="s">
+        <v>12</v>
+      </c>
+      <c r="B668" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C668" s="2">
+        <v>11</v>
+      </c>
+      <c r="D668" s="3">
+        <v>8.658008658008658E-3</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4">
+      <c r="A669" t="s">
+        <v>12</v>
+      </c>
+      <c r="B669" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C669" s="2">
+        <v>12</v>
+      </c>
+      <c r="D669" s="3">
+        <v>8.5106382978723406E-3</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4">
+      <c r="A670" t="s">
+        <v>12</v>
+      </c>
+      <c r="B670" s="2">
         <v>2026</v>
       </c>
-      <c r="C665" s="2">
+      <c r="C670" s="2">
+        <v>1</v>
+      </c>
+      <c r="D670" s="3">
+        <v>2.7972027972027972E-3</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4">
+      <c r="A671" t="s">
+        <v>12</v>
+      </c>
+      <c r="B671" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C671" s="2">
+        <v>2</v>
+      </c>
+      <c r="D671" s="3">
+        <v>1.4265335235378032E-3</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4">
+      <c r="A672" t="s">
+        <v>12</v>
+      </c>
+      <c r="B672" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C672" s="2">
         <v>3</v>
       </c>
-      <c r="D665" s="3">
+      <c r="D672" s="3">
         <v>2.5706940874035988E-3</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4">
+      <c r="A673" t="s">
+        <v>12</v>
+      </c>
+      <c r="B673" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C673" s="2">
+        <v>5</v>
+      </c>
+      <c r="D673" s="3">
+        <v>3.9840637450199202E-3</v>
       </c>
     </row>
   </sheetData>

--- a/upload/taxa-readmissao-2025.xlsx
+++ b/upload/taxa-readmissao-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
